--- a/llm-classifier/results/llm_results_llama3.1_8b.xlsx
+++ b/llm-classifier/results/llm_results_llama3.1_8b.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N228"/>
+  <dimension ref="A1:N249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,7 +560,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-04-25T17:36:56+00:00</t>
+          <t>2026-04-26T16:34:15+00:00</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-04-25T17:36:59+00:00</t>
+          <t>2026-04-26T16:34:18+00:00</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -669,10 +669,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The project aims to develop an architecture for integrating medical data, including images stored in the DICOM standard, using a wrapper that allows access to specific attributes and enables semantic annotation of images.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>The project aims to develop an ontology-based system for medical data retrieval, using the DICOM standard.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ontologías, Recuperación de información, Imágenes médicas, DICOM</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Bases de datos</t>
@@ -690,7 +694,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-04-25T17:37:03+00:00</t>
+          <t>2026-04-26T16:34:21+00:00</t>
         </is>
       </c>
     </row>
@@ -727,7 +731,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>The project involves developing a system for managing personnel and physical resources of the Tuluá Firefighters Corps, which suggests a management application for a specific organization.</t>
+          <t>The project involves developing a system for managing personnel and physical resources of the Tuluá Fire Department, which suggests a management application for a specific organization.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -752,7 +756,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-04-25T17:37:07+00:00</t>
+          <t>2026-04-26T16:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -779,12 +783,30 @@
 Como resultado se presenta la aplicación web PrediXaber11, donde las personas pueden acceder y ejecutar consultas. La aplicación usará la información suministrada del evaluado para entregar los posibles resultados en cada una de las áreas académicas evaluadas por el ICFES.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Data mining</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>The project involves applying data mining techniques to predict results in the Saber 11 tests, using historical data from the ICFES databases.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Data mining, Saber 11</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Minería de datos</t>
@@ -800,7 +822,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:34:27+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -823,12 +849,30 @@
           <t>En la actualidad las empresas utilizan gran cantidad de información, siendo un componente fundamental para las mismas [Pl99]. Las fuentes de datos son múltiples, y debido al crecimiento tecnológico global, enfáticamente en las ciencias de la computación, las redes sociales se han convertido en un recurso de gran importancia para las organizaciones [ELGF07]. La información que se encuentra en las redes sociales sobre compañías en particular, no solo es importante para ellas, sino también indispensable para las que usan dicha información como insumo para realizar análisis de mercado, imagen, preferencias, etc. [BSH09]. Por ejemplo, en Bogotá hay una empresa llamada Meridean que realiza estudios de Social Media para otras corporaciones a partir de información extra ‘ida de las redes sociales. El presente trabajo de grado, propone como solución, la construcción de un prototipo de clasificador semi-supervisado de texto, que ayudaría a automatizar (evitar labores manuales costosas y demoradas) el proceso de clasificación de información en la compañía. A partir de características (features) de los datos (comentarios de social media), el prototipo entrega los mismos, clasificados por categorías. Estas anotaciones obedecen a parámetros establecidos por Meridean. Para verificar la aplicabilidad del sistema, se realizaron pruebas de rendimiento al clasificador, las cuales se detallan en este documento.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Information systems</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>The project proposes a semi-supervised text classifier for social media comments, which is an information-handling system that does not fit any narrower term.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Redes sociales, Comentarios, Clasificación</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -844,7 +888,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:34:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -868,12 +916,30 @@
 </t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>The project aims to improve content management in the academic coordinations of Universidad del Valle Sede Caicedonia through a web-based platform for enterprise content administration, which supports the main tasks of digital content lifecycle.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Administración de contenidos digitales, Sistemas de información Web</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -889,7 +955,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:34:33+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -912,12 +982,30 @@
           <t>Actualmente, la empresa Carvajal Tecnología y Servicios, tiene una serie de insuficiencias en la dependencia de tercerización de tecnología y outsourcing (ITO), donde se brindan servicios para satisfacer necesidades internas y a diferentes sectores de la industria, siendo la inducción a nuevos empleados y la operación del servicio, las problemáticas identificadas. En este sentido, actualmente dicha dependencia no dispone de un conducto regular sólido que le permita estructurar una capacitación de forma eficiente para los empleados nuevos. Además, en la operación del servicio no se cuenta con información centralizada, ocasionando pérdida de tiempo, reprocesos e incremento de los costos del negocio. En consecuencia, una posible solución a la problemática planteada es centralizar la información en un gestor de contenidos, apoyado en una plataforma tecnológica, con lo que al mismo tiempo, se apoyarán los procesos de gestión del conocimiento que internamente adelanta la empresa.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>The project aims to adapt a commercial platform of open code to meet the needs of Carvajal Technology and Services in terms of content and learning, as support for knowledge management processes.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Tercerización de Tecnología y Outsourcing (ITO), Gestión del conocimiento, Plataforma virtual</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -933,7 +1021,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:34:37+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -957,12 +1049,30 @@
 </t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>The project developed a web application for iridologists to support the diagnosis of diseases through iris interpretation, using agile development and computer vision techniques.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Medicina alternativa, Diagnóstico de enfermedades</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Procesamiento digital de imagenes</t>
@@ -978,7 +1088,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:34:40+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1001,12 +1115,30 @@
           <t>El principal objetivo de una arquitectura SSO (Single Sign On) es transferir la funcionalidad de autenticación propia de cada programa a un solo servicio de SSO. En una arquitectura SSO, todos los mecanismos de seguridad se encuentran concentrados en el SSO, siendo éste el único punto de autenticación en el sistema. Otro beneficio de una arquitectura Single Sign On es que los usuarios deben hacer el proceso de ingreso una sola vez a cada aplicación, a pesar de que continúan interactuando con múltiples componentes de seguridad en el sistema. El concepto Single Sign On no necesariamente se refiere a una sincronización de contraseñas, ya que en ese caso todas las aplicaciones y servicios funcionarían con una misma contraseña, pero no es una buena solución, ya que en lugar de fortalecer la seguridad, la estaría debilitando. Una implementación real de SSO, deberá contar con un agente SSO que se encarga de almacenar en una base de datos o directorio protegido los passwords que le permiten al usuario acceder a cada una de las aplicaciones o servicios, en el momento que lo desee, ya que el proceso de login se realiza de manera transparente al usuario, una vez que éste ha sido autenticado por medio de una arquitectura SSO.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>The project focuses on a centralized system for authentication and authorization, which is a key aspect of cybersecurity.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Autenticación, Autorización, Seguridad en los computadores</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Seguridad</t>
@@ -1022,7 +1154,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:34:43+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1045,12 +1181,30 @@
           <t>El preprocesamiento de información tiene como propósito fundamental la “manipulación y transformación de los datos en bruto de manera que permita exponer o al menos facilitar la exposición de la información contenida en el arreglo de datos. [1]” Existen diversas herramientas que ofrecen la posibilidad de ejecutar subtareas de la extracci´on de informaci´on y procesamiento de lenguaje natural con este propósito, sin embargo son escasas aquellas que brindan la posibilidad de ejecutar más de una de estas tareas, esto sin mencionar que del mismo modo son escasas aquellas que permiten el tratamiento de datos en idiomas diferentes al inglés. Tomando como fuente de datos a procesar a Internet, debe considerarse que es una fuente inagotable de información, basta y no muy bien ordenada; no obstante dicha información debe tener cierto grado de orden para poder ser tratada por las subtareas de extracci´on de informaci´on y generar resultados útiles a partir de los datos procesados, como por ejemplo en el área del marketing para mejorar ventas o productos, analizar tendencias, entre otros. En el presente documento se expone el proceso de desarrollo de una aplicación que integra diferentes herramientas de preprocesamiento de información adaptadas para el idioma espa˜nol que toma como datos de entrada texto recuperado de la red social Twitter. Inicialmente se implementa un módulo que permite recuperar los documentos usando palabras clave como criterio de búsqueda. Así mismo se detalla la implementaci´on de m´odulos de corrección de palabras mal escritas, eliminaci´on de palabras vac´ıas, anotación gramatical, reconocimiento de nombres de entidades y el proceso realizado en su integración.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Information systems</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>The project aims to develop a framework for processing text extracted from Twitter, which involves integrating different tools for pre-processing information in Spanish. This is an example of an information system that handles and transforms raw data.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Framework, Procesamiento de textos, Twitter</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Procesamiento de lenguaje natural</t>
@@ -1066,7 +1220,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:34:46+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1089,12 +1247,30 @@
           <t>La programación por restricciones presenta estrategias de solución a problemas de optimización y combinatorios. La estrategia general para su uso es mediante la especificación de las variables del problema y las relaciones (restricciones) que entre ellas se deben mantener. Después de dicha especificación el usuario hace uso de motores de búsqueda predefinidos que se encargan de recorrer el espacio de soluciones del problema. Gecode es un componente de software que implementa el paradigma de programación por restricciones de manera eficiente. Sin embargo su utilización es compleja para usuarios por el lenguaje de programación. Oz es un lenguaje de programación inventado en la década de los 90 que soporta entre otros el paradigma de programación por restricciones. Debido a su concepción multiparadigma ha sido adoptado por una comunidad de investigación importante. Este lenguaje interpretado ofrece mejores abstracciones y provee un ambiente de trabajo más confortable. Su implementación, Mozart hasta ahora ha carecido de soporte en la adopción de los avances en la investigación en esta ´área. Por esta razón se ha diseñado una nueva máquina virtual con Gecode como motor de restricciones, para tomar ventaja de estos avances. En este documento se propondrán los mecanismos para la interacción de los motores de búsqueda implementados en Gecode con Mozart, como también los mecanismos que permitan al usuario implementar sus propios motores de búsqueda en Oz y utilizarlos. Esto es de gran importancia para los usuarios porque permitirá sacar ventaja del conocimiento que este posee sobre el problema obteniendo búsquedas más eficientes.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Constraint programming</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>The project involves implementing search mechanisms for a new virtual machine using Gecode, a constraint programming engine, to take advantage of recent advances in the field.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Programación con restricciones, Motores de búsqueda, Gecode</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Programación por restricciones</t>
@@ -1110,7 +1286,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:34:50+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1133,12 +1313,30 @@
           <t>El presente documento describe el proceso realizado en torno al desarrollo de un trabajo de grado que tiene como propósito la implementación de una aplicación e-Learning 2.0 diseñada bajo conceptos de usabilidad y adaptabilidad. Aplicación que estará orientada a organizaciones de cualquier sector económico, que involucren procesos de formación y/o capacitación dentro de su planeación estratégica y sus objetivos misionales y visionales, de tal forma que éstas puedan adaptar y mantener su propia plataforma con base en sus necesidades, reduciendo así las barreras presentes en torno a las limitaciones geográficas que representan un aspecto importante para las organizaciones.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>The project title and abstract clearly indicate the development of an e-Learning application for organizations, focusing on usability and adaptability.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>e-Learning, Usabilidad, Adaptabilidad</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1154,7 +1352,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:34:53+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1178,12 +1380,30 @@
 </t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>The project involves developing a software tool for educational purposes, specifically to support students in learning fractions. The tool includes an Object Virtual of Learning (OVA) and allows configuration of evaluations, making it a type of Learning Management System (LMS).</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Educación básica primaria, Objetos Virtuales de Aprendizaje (OVA), Sistema de Gestión de Aprendizaje (LMS)</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -1199,7 +1419,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:34:57+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1223,12 +1447,30 @@
 </t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>The project aims to develop a tool for facilitating the construction of scenarios for 2D video games, which is a key aspect of game development. The focus on game development and scenario creation suggests that this is a serious game project.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Videojuegos, Desarrollo de software</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Juegos serios</t>
@@ -1244,7 +1486,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:35:01+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1267,12 +1513,30 @@
           <t>La Universidad del Valle sede Tuluá tiene la necesidad de disponer de un sistema de información para apoyar los procesos involucrados en el desarrollo del programa de práctica y/o pasantías para los estudiantes; se requiere de un herramienta que sirva como punto de confluencia en el establecimiento de relaciones con los diferentes actores que participan en la prestación de los servicios. Aunque las prácticas profesionales se formalizan a través de contratos de aprendizaje o convenios de práctica o pasantía, entre la universidad y la entidad externa, es indispensable apoyar el proceso a través de un sistema que permita centralizar la información de ofertas de las empresas, hojas de vida académicas de los estudiantes, además de dinamizar las tareas, mejorar la prestación del servicio apoyando las actividades de supervisión de los estudiantes en su primera experiencia laboral. Para solucionar exitosamente el problema, se hizo necesario realizar un proceso de ingeniería de software, en el que se analizaron cuáles serían la metodología y el modelo de desarrollo más adecuados según el procedimiento estándar definido por la Universidad del Valle y la dificultad que se quería resolver. Se decidió implementar un sistema de información web que permitiera a los diferentes actores interactuar y compartir de manejar fácil y eficazmente la información generada durante del proceso de consecución y desarrollo de las pasantías o prácticas profesionales. Posteriormente se realizaron las respectivas fases de análisis, diseño, implementación, pruebas y puesta en marcha del sistema siguiendo los lineamientos del modelo de desarrollo seleccionado. Finalmente se concluyó que con un sistema de información web para el apoyo a las pasantías y prácticas de los programas de pregrado de la Universidad del Valle sede Tuluá logra brindar una solución efectiva a la problemática presentada, obtenido resultados satisfactorios para los diferentes usuarios. Este documento sintetiza el trabajo realizado durante el desarrollado del proyecto.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>The project aims to develop a web-based system for managing professional practices and internships at Universidad del Valle Sede Tuluá, which is a management application for the university.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Sistemas de información, Desarrollo de software</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1288,7 +1552,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:35:04+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1313,7 +1581,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1327,7 +1595,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>The project aims to develop an application for the Hospital Psiquiátrico Universitario del Valle's cost system, implementing the ABC methodology and standardizing processes to improve results and data gathering.</t>
+          <t>The project aims to develop an application for the Hospital Psiquiátrico Universitario del Valle to implement the ABC cost method, which is a management system for a specific organization.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1352,7 +1620,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-04-25T17:37:54+00:00</t>
+          <t>2026-04-26T16:35:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1645,30 @@
           <t>En este documento se detalla el proceso realizado como trabajo de grado consistente en la sistematización del control de asistencia docente de la Universidad del Valle sede Tuluá, el cual actualmente maneja el registro de los horarios, observaciones, cronogramas, reportes y el seguimiento del estado de las asistencias de los docentes de manera manual. Esta información se encuentra descentralizada, es difícil de administrar y el proceso es lento y dispendioso desperdiciando tiempo y recursos. Esta propuesta busca dar solución a los problemas anteriormente mencionados en el control de asistencia docente que opera en la Universidad, mediante la incorporación de un sistema de reconocimiento dactilar que registra y verifica las huellas de los docentes y permite su identificación única, garantizando la presencia del profesor a sus horas de clase. El sistema de reconocimiento dactilar se sincroniza con la plataforma informática encargada de la gestión del control de asistencia docente en la Universidad. Se generan reportes desde la aplicación con sus respectivos formatos de calidad para así facilitar el seguimiento y cumplimiento del cronograma de los docentes y aprovechar al máximo el uso de este aplicativo.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>The project aims to develop a solution for the University's attendance control process, incorporating biometric recognition and integrating with an existing platform.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Control de asistencia docente, Lector biométrico</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1398,7 +1684,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:35:11+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1422,12 +1712,30 @@
 </t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>The project aims to create a social network for job and academic opportunities, connecting the University of Valle Sede Tuluá with its graduates and employers. This is an enterprise-level application that manages interactions between stakeholders.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Redes sociales, Egresados, Universidad del Valle</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1443,7 +1751,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:35:15+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1466,12 +1778,30 @@
           <t>Los procesos de selección de personal cada vez son más importantes para los empresarios que siempre buscan tomar decisiones adecuadas al momento de vincular personal a sus instituciones, la gran cantidad de aspirantes propicia que dicho proceso esté rodeado por un gran volumen de información que casi siempre se encuentra en medios físicos y por ende ocasiona demoras, confusión o desorganización en el proceso. Este trabajo se realiza con el fín de dar solución a problemas reales que se presentan en las actividades de reclutamiento y selección de personal dentro de las empresas, proporcionando un sistema de información web que además de sistematizar los mencionados procesos tiene la característica de recomendar aspirantes sin que se quiera desplazar el criterio humano de expertos o encargados de llevar a cabo actividades del proceso. Con base en lo anterior se plantea una solución combinando diversos conceptos y tecnologías, entre los aspectos más relevantes por mencionar se comenta que se integra el sistema de información web mencionado anteriormente con agentes de software que tienen como comportamiento principal generar una recomendación de aspirantes que se adhieran a un perfil determinado, también es importante mencionar que los agentes implementados aplican lógica difusa para producir su recomendación, de modo que con esto se logra eliminar subjetividades y sesgos que normalmente afectan negativamente las decisiones en un proceso de selección. Otros aspectos, tecnologías y conceptos para la realización de este proyecto se detallarán más adelante.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Recommender systems</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>The project aims to develop a web-based system that recommends candidates for selection based on software agents, which apply fuzzy logic to eliminate subjectivities and biases.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sistemas de recomendación Web, Reclutamiento de personal</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1487,7 +1817,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:35:18+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1513,7 +1847,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1527,12 +1861,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>The project involves the design and implementation of a CRM system for Contact Center Alopolis SAS, which is a management application for a specific organization.</t>
+          <t>The project involves the design and implementation of a CRM system for Contact Center Alopolis S.A.S., which is a management application for a specific organization, making it an Enterprise Information System.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>CRM, arquitectura, mercadeo, ventas, desempeño</t>
+          <t>CRM, Plataforma digital, Contact Center Alopolis S.A.S., Mercadeo, Ventas</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1552,7 +1886,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-04-25T17:38:04+00:00</t>
+          <t>2026-04-26T16:35:22+00:00</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1913,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1593,12 +1927,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>The project involves the development of a CRM system for Contact Center Alopolis SAS, which is an enterprise-level application that manages customer relationships and interactions.</t>
+          <t>The project involves the development of a web application for a specific organization, Concesionario Automotores Bejarano, to manage its services and inventory in a more clear and organized way.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>CRM, arquitectura, mercadeo, ventas, desempeño</t>
+          <t>Aplicaciones Web, Sistemas de gestión de información, Sistemas de gestión</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1618,7 +1952,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-04-25T17:38:09+00:00</t>
+          <t>2026-04-26T16:35:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1994,30 @@
 tiempo establecido.</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>The project aims to implement a web-based system for La Inversora La 21, managing vehicle location and information, which is a typical enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Sistemas de información, Gestión de información</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -1681,7 +2033,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:35:29+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1704,12 +2060,30 @@
           <t>El presente trabajo de grado tiene como objetivo implementar una herramienta que ayudará a fortalecer el proceso de aprendizaje de los niños con problemas de Discalculia (dificultad en el aprendizaje de las matemáticas) del CEET (Centro Educación Especial Tuluá) a través de una aplicación educativa web. En cumplimiento a este objetivo, se realizó una investigación acerca de las metodologías de enseñanza en niños con este problema, de igual forma se realizaron reuniones y se entrevistaron especialistas los cuales asesoraron de forma correcta el procedimiento que se debía realizar en la elección de la metodología indicada. Igualmente es importante destacar el uso de las TIC (Tecnologías de la información y comunicación) como herramientas de apoyo dando cumplimiento al objetivo del presente trabajo de grado. Por tal motivo se elaboraron OVAs (Objetos Virtuales de Aprendizaje), un sistema de recomendación donde se definió las rutas de aprendizaje de los niños y para la administración de la información de los usuarios y los OVAs, se realizó un LMS (Sistema de Gestión de Aprendizaje) manejando principios de diseño web y por ende asegurando el cumplimiento de principios básicos de navegabilidad, usabilidad y accesibilidad, garantizando que la interacción del usuario con ésta sea lo más agradable posible. Todo el proceso de elaboración de la aplicación se basó siguiendo una metodología de desarrollo ágil apropiada para asegurar todas las entrega en el tiempo establecido.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>The project aims to develop a web-based educational tool for children with dyscalculia, using virtual learning objects and a learning management system. This is an e-learning artifact without a dedicated game loop.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>E-learning, Virtual Learning Objects (OVA), Learning Management System (LMS)</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -1725,7 +2099,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:35:33+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1748,12 +2126,30 @@
           <t>Actualmente las empresas ya no se encuentran bajo el enfoque industrial, donde lo importante eran los activos físicos o tangibles, ahora se debe invertir esfuerzos en obtener y potenciar los activos intangibles; teniendo en cuenta que actualmente se vive en la era del conocimiento, donde los datos, la información y por ende la comunicación han pasado a ser determinantes en el éxito o fracaso de la gestión empresarial [34]. En consecuencia, la competitividad de las empresas está directamente relacionada con una buena gestión, donde la pregunta sería entonces ¿Cómo realizar una buena gestión?. El Balanced Scorecard (BSC) es un revolucionario método que apoya el proceso de gestión empresarial, dónde además de tener en cuenta la perspectiva financiera, también tiene en cuenta a los clientes, los procesos, la formación y crecimiento [34]. En este sentido, el presente proyecto ejecutado en modalidad de pasantía en la empresa Clip Consulting, permitió construir un producto de software que permitiera crear y administrar un BSC como apoyo al proceso de gestión empresarial, el cual será puesto en el mercado para los clientes de la empresa en cuestión.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>The project develops a web application based on the Balanced Scorecard method to support strategic planning and improve productivity in companies, which is a classic example of an enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Balanced scorecard (Gestión estratégica), Planificación estratégica</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1769,7 +2165,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:35:36+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1792,12 +2192,30 @@
           <t>Actualmente, la mayoría de empresas cuentan con Sistemas de Información Transaccionales para apoyar los procesos que ejecutan y gestionan cotidianamente. Pero, aunque las empresas posean un Sistema de Información Transaccional, sólo una minoría está consciente del valor de la información registrada por dichos Sistemas de Información, la cual puede ser utilizada por personas con cargos gerenciales para tomar así decisiones concernientes con el mejoramiento de procesos internos de la empresa como también determinaciones que a futuro dirijan el rumbo de la misma. Por lo anterior, surgieron los Sistemas de Información para el apoyo a la toma de decisiones, también conocidas como Aplicaciones de Inteligencia de Negocios, las cuales suplen la necesidad de los gerentes de poseer una herramienta que analice la información registrada en las bases de datos de los Sistemas de Información Transaccionales, para que las decisiones que tomen dichos gerentes tengan una mejor base y no solo sea una simple intuición. En el desarrollo de este proyecto se realizó un estudio en conjunto con la persona encargada de la toma de decisiones de las áreas de venta y mercadeo para elegir un conjunto de indicadores de desempeño claves para medir puntos de rendimiento que se determinaron como esenciales para su monitoreo. De manera paralela se fue desarrollando una aplicación web responsiva, la cual cuenta con una interfaz hecha con HTML5, siendo esto una característica que ayuda al desarrollo de software más simplificado de dicha interfaz. En conjunto, estos dos elementos brindan un apoyo a la toma de decisiones respecto a las áreas de venta y mercadeo del Call Center de la empresa BCS.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>The project is a management application for the sales and marketing areas of the company BCS, with a web-based interface using HTML5. The system aims to support decision-making by analyzing data from transactional information systems.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sistemas de información en administración, Sistemas de información Web, Inteligencia de negocios</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1813,7 +2231,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:35:40+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1836,12 +2258,30 @@
           <t>La Gestión del Conocimiento es un concepto aplicado en las organizaciones, que pretende transferir el conocimiento y experiencias existentes entre sus miembros, de modo que pueda ser utilizado como un recurso disponible para otros en la organización. Cualquier institución educativa puede verse como una organización que tiene como fin la educación y la formación académica, donde constantemente maneja un flujo de información, el cual representa un activo intangible muy valioso que en la mayoría de los casos no es correctamente gestionado. La plataforma que se desarrollará apoyará el proceso de gestión de conocimiento facilitando técnicas para capturar, organizar y almacenar el conocimiento que fluye en el colegio San Francisco de Asís, para transformarlo en un activo intelectual que represente beneficios académicos y se pueda compartir con cualquier persona. De esta manera se generará una comunidad virtual que permitirá que se mejoren las relaciones docente-estudiante, promueva la interacción social, el aprendizaje colaborativo y se administren correctamente todas las habilidades y experiencias tanto de docentes como de estudiantes haciendo del aprendizaje un proceso más ameno e interactivo.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>The project aims to develop a web platform that supports the knowledge management process in the San Francisco de Asís College, focusing on creating a virtual community. This is a management application for a specific organization (the college), which aligns with the definition of Enterprise information systems.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Plataforma Web, Gestión del conocimiento</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1857,7 +2297,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:35:44+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1881,12 +2325,30 @@
 </t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>The project aims to develop a software system for the management of undergraduate projects and anteprojects at Universidad del Valle Sede Tuluá, which is a specific organization.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sistemas de información para la gestión, Proyectos de grado, Anteproyectos de grado</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1902,7 +2364,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:35:48+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1926,12 +2392,30 @@
 </t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>The project aims to develop a CRM system for C.E.A. Auto Ríos, which is an enterprise-level application that will manage customer relationships and operational processes.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>CRM, TIC, Sistemas de información Web</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1947,7 +2431,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:35:51+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1970,12 +2458,30 @@
           <t>El propósito de este proyecto surgió de la necesidad de la Empresa Ingenio Carmelita S.A para controlar los activos de información que se manejan en la compañía y además de dar una solución correcta para aquellos activos de información más susceptibles a incidentes como lo son los de hardware y software. Por medio de la metodología de desarrollo RUP (Rational Unified Process) se realizaron las diferentes actividades que permitieron la identificación de los activos y de los diferentes incidentes a los que están expuestos estos, posteriormente se realizó el proceso de diseño y construcción de la aplicación que permitiera suplir los requisitos planteados. Para lo anterior se logró construir una aplicación web con la capacidad de gestionar los activos de información de la empresa de una forma fácil y eficiente, y el cual permitió guardar en la bases de datos de la empresa la referencia de los activos importantes, así como el control de la trazabilidad o movimientos de los mismos. Además permite el registro y respuesta a los incidentes de hardware y software logrando llevar un control sobre estos incidentes.</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>The project aims to develop a web-based system for the company Ingenio Carmelita S.A. to manage its assets, including hardware and software, using the RUP methodology.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Activos de información, Hardware, Software</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -1991,7 +2497,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:35:54+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2015,12 +2525,30 @@
 </t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>The project involves the development of a software system for COFINCAFE, a cooperative in the solidary economy sector, to facilitate management and decision-making using Balanced Scorecard methodology.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Balanced scorecard, Sistemas de gestión</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2036,7 +2564,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:35:58+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2060,12 +2592,34 @@
 Además, la aplicación web utiliza un agente de recomendación que es capaz de soportar las fases del proceso de compra al ayudar a los clientes a realizar sus pedidos por medio de recomendaciones de productos. Este agente, hace uso de sistemas de filtrado colaborativo, que utilizan elementos como: la totalidad de los productos que se ofrecen, historiales de compras propios y de otros usuarios, similitudes entre los perfiles de usuarios y correlación entre los diferentes productos, los cuales son necesarios para el cálculo de recomendaciones y similitudes de un conjunto de productos [2, 29].</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Recommender systems</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>The project developed a web application for managing restaurant orders, which includes a recommender agent that uses collaborative filtering to suggest products based on user profiles and purchase history.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Aplicaciones informáticas, Sistemas de recomendación Web</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Sistemas de recomendación</t>
@@ -2081,7 +2635,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:36:01+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2105,12 +2663,30 @@
 </t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>The project aims to design and implement a web-based system for managing requests and complaints from clients, providers, and employees of Carvajal Tecnología y Servicios' contracting companies, which indicates an enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sistemas de información, Sistemas de información Web</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2126,7 +2702,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:36:04+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2150,12 +2730,30 @@
 </t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>The project developed a system for the Universidad del Valle Sede Buga to manage academic programming, attendance control, and faculty nomination, which is a management application for a specific organization.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sistemas de información, Programación académica, Nómina docente</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2171,7 +2769,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:36:08+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2195,12 +2797,30 @@
 </t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>The project involves the development and implementation of a system to support process management for Conectic S.A.S, which is an enterprise-level application.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sistemas de información, Gestión de procesos</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2216,7 +2836,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:36:11+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2244,7 +2868,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2258,12 +2882,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>The project uses a genetic algorithm to solve the problem of scheduling appointments, which is a classic example of artificial intelligence. The use of techniques such as selection, crossover, and mutation also supports this classification.</t>
+          <t>The project uses genetic algorithms, a technique in artificial intelligence, to solve the problem of scheduling.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Algoritmos genéticos, Inteligencia Artificial</t>
+          <t>Algoritmos genéticos, Asignación de agendas</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2283,7 +2907,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-04-25T17:39:43+00:00</t>
+          <t>2026-04-26T16:36:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2934,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2324,12 +2948,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>The project focuses on developing a motion estimation model using parallel programming with OpenCL framework, which is a software engineering task.</t>
+          <t>The project focuses on developing a parallel programming approach for HEVC video coding, which is a software engineering task.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>motion estimation, parallel programming, OpenCL</t>
+          <t>Programación paralela, Estimacion de movimiento, High Efficiency Video Coding (HEVC), Graphics Unit Processor (GPU), C++</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2349,7 +2973,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-04-25T17:39:47+00:00</t>
+          <t>2026-04-26T16:36:17+00:00</t>
         </is>
       </c>
     </row>
@@ -2377,7 +3001,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2391,12 +3015,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>The project aims to enhance the semantic content of a Learning Management System (LMS) by integrating it with Linked Data, which is a key aspect of information systems.</t>
+          <t>The project aims to enhance the semantic content of a Learning Management System (LMS) by linking it with open data from the Web of Data, which is a key aspect of information systems.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Web de Datos, Sistemas de Gestión de Contenidos, Datos Enlazados Abiertos</t>
+          <t>Administración de contenidos Web, Web Semántica, Sistemas de información Web</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2416,7 +3040,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-04-25T17:39:52+00:00</t>
+          <t>2026-04-26T16:36:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2442,12 +3066,30 @@
 </t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>The project involves designing and implementing a software tool for educational support, accessible through a webpage, to enhance language skills in primary school students.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Software de aplicación, Software educativo, Servicios de apoyo académico</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -2463,7 +3105,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:36:24+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2487,12 +3133,30 @@
 </t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>The project is a management application for the Universidad del Valle Sede Tuluá, supporting the evaluation process of its teachers. The system uses Django and Python to provide statistical analysis and reporting tools.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sistemas de información, Evaluación de personal docente</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2508,7 +3172,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:36:27+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2532,12 +3200,30 @@
 </t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>The project aims to develop and implement a system that automates administrative processes for the Urban Curatorship of Tuluá, providing web-based access to information on license applications.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Automatización de procesos, Procesos administrativos, Curadurías urbanas</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2553,7 +3239,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:36:31+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2577,12 +3267,30 @@
 </t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>The project aims to automate processes for SISA Soluciones Integrales En Salud, a private healthcare provider, which suggests it is an enterprise-level application.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Automatización de procesos, Sistemas de información</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2598,7 +3306,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:36:34+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2622,12 +3334,30 @@
 </t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>The project is a management application for the Cámara de Comercio de Tuluá, supporting their quality management system with features such as format administration, action plan tracking, and indicator presentation.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Sistema de Gestión de Calidad (SGC), Indicadores de gestión</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -2643,7 +3373,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:36:37+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2709,7 +3443,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-04-25T17:40:14+00:00</t>
+          <t>2026-04-26T16:36:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2781,7 +3515,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-04-25T17:40:17+00:00</t>
+          <t>2026-04-26T16:36:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2816,7 +3550,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2830,7 +3564,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>The project aims to support and facilitate the learning process of students in the programs of Ingeniería de Sistemas and Tecnología en Sistemas de Información at Universidad del Valle, through a web application that supports virtual teaching-learning processes.</t>
+          <t>The project aims to support the formation dynamics inherent to the algorithm of the Systems Engineering and Information Technology in Systems programs at Universidad del Valle - Sede Tuluá through virtual teaching-learning processes, which is a key aspect of e-learning.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2855,7 +3589,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-04-25T17:40:21+00:00</t>
+          <t>2026-04-26T16:36:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2888,12 +3622,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Enterprise information systems</t>
+          <t>Information systems</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2902,12 +3636,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>The project aims to design and implement an application for optimizing public transportation routes using constraint programming, which is a management application for a specific organization (the municipality of Tuluá). The novelty lies in the use of this paradigm for Transit Network Design.</t>
+          <t>The project aims to optimize routes for public transportation using constraint programming, which is a key aspect of information systems.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Transporte público masivo, programación por restricciones</t>
+          <t>Transporte público, Rutas, Optimización de rutas</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2927,7 +3661,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-04-25T17:40:26+00:00</t>
+          <t>2026-04-26T16:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2998,7 +3732,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-04-25T17:40:28+00:00</t>
+          <t>2026-04-26T16:36:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3031,12 +3765,30 @@
           <t>Actualmente se destacan muchas empresas dentro del sector de consultoría ambiental, las cuales prestan servicios profesionales y se encargan de asesorar a otras empresas en una o muchas áreas especificas que comprende el estudio de emisión de gases atmosféricos, calidad del aire, aguas residuales, ruido, entre otros. Estas empresas llevan a cabo un proceso de planeación para realizar la prestación de este servicio, con el fin abarcar detalladamente este proceso se tomó como referencia la empresa Incoambiental S.A.S. Con el objetivo de apoyar la prestación de este servicio y sus actividades en la planeación del mismo. Debido a que algunas de las tareas como la asignación de la consultoría se lleva actualmente de forma manual y la información no está centralizada, esto produce pérdida de tiempo, costos adicionales, realización de tareas que no son necesarias y reprocesos. Para la problemática planteada anteriormente se propuso la implementación de un sistema de información web para empresas que brindan el servicio de consultoría, con el fin de apoyar el proceso de planeación en la prestación del mismo, esta aplicación facilita la organización en las actividades que deben realizar los encargados de este servicio, el acceso a los formatos requeridos para este proceso, el control de los elementos que pertenecen al área de almacén, igualmente la generación de reportes para seguimiento de las actividades.</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>The project aims to implement a web-based system for Incoambiental S.A.S. to support the planning of operations and inventory management, which is a specific organization's management application.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Consultoría de empresas</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3052,7 +3804,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:36:58+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3082,7 +3838,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3096,10 +3852,14 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>The project presents Ecclesia, a web-based information system for parochial process management that combines administrative functions, event tracking, student follow-up, and income determination. The system is designed to reduce response times in parochial processes and assist in decision-making by displaying content information promptly.</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>The project is a management application for the Parroquia San Martín de Porres, combining administrative functions, event tracking, and income determination. The system aims to reduce response times and improve decision-making.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sistemas de Información Administrativa, Gestión de procesos; Control de actividades</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3117,7 +3877,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-04-25T17:40:50+00:00</t>
+          <t>2026-04-26T16:37:02+00:00</t>
         </is>
       </c>
     </row>
@@ -3148,12 +3908,30 @@
           <t>El presente proyecto se basó en una problemática que se genera alrededor de la gestión de los libros reglamentarios, la cual permite evidenciar en su desarrollo un considerable esfuerzo de parte de los docentes, dado que dicha gestión se realiza de forma manual ao a través de herramientas ofimáticas. Este proceso es costoso en tiempo e ineficiente. El análisis es lento, difícil y propenso a errores por lo que no permite identificar problemas y mucho menos oportunidades de mejoramiento por parte de los docentes y directivos docentes, dicha problemática está presente en la Institución Educativa María Antonia Ruiz. Para dar solución al problema propuesto se realizó el análisis, diseño e implementación de un sistema de información compuesto de una aplicación desktop, aplicación móvil y aplicación web para los procesos de libros reglamentarios, todo esto relacionado con la programación académica de la Institución. El proyecto se desarrolló basado en la metodología ICONIX y el patrón arquitectónico Modelo-Vista-Controlador (MVC), permitiendo así la creación de componentes robustos a su vez permitiendo la escalabilidad del mismo. También facilitó la realización de pruebas a lo largo del proceso y garantizando un producto final que cumpliera con las funcionalidades requeridas, ofrece mecanismos para la gestión de año lectivo, la gestión de planes de aula, diarios de clase y novedades en el aula.</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>The project developed a system to manage the institution's regulatory books, which is a management application for a specific organization.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Aplicaciones móviles, Libros reglamentarios</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3169,7 +3947,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:37:05+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3197,12 +3979,30 @@
           <t>En la empresa Área Informática S.A.S, se llevaban a cabo muchos procesos de forma manual, esto conllevó a retrasos y descontrol sobre la información que se generaba en los diferentes procedimientos. Se vio entonces, la necesidad de ayudar a mejorar estos procesos aportando los conocimientos adquiridos, buscando mejoras significativas en función de la calidad. Se realizó un análisis, diseño e implementación para un sistema de información el cual ayudó a la empresa a gestionar los procesos relacionados con las órdenes de servicio, se desarrolló un mecanismo el cual permitió generar la agenda de trabajo partiendo de la prioridad de los servicios que solicitan los clientes y de la disponibilidad de los técnicos, con la posibilidad de generar reportes estadísticos, sobre el estado de los procesos de Área Informática S.A.S. Y de esta forma mejorar la calidad en los procesos que se llevan a cabo en esta empresa.</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="H53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>The project aims to develop an information system for the company Area Informática S.A.S, specifically for managing service orders and improving processes.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sistemas de información en administración, Órdenes de servicio</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3218,7 +4018,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:37:08+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3248,12 +4052,30 @@
           <t>En el presente documento se muestra el desarrollo de una herramienta de software diseñando e implementando objetos virtuales de aprendizaje (OVA) como apoyo al proceso de enseñanza-aprendizaje del programa de Manejo Ambiental para los estudiantes de grado once de la Institución Educativa Técnica La Marina en el área de Desechos de Producción Agropecuaria; este trabajo involucró la implementación del sistema de aprendizaje (LMS) Chamilo, que permitió alojar y acceder a diferentes actividades de aprendizaje independientes en varios formatos. Además, este ofrece mecanismos para la gestión de usuarios, grupos, cursos, colecciones y/o notas generadas por la interacción de los estudiantes con la evaluación de los OVA implementados.</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>The project involves the development of a software tool to support teaching and learning in the context of environmental management, using virtual objects of learning (OVA) and an LMS system.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>E-learning, Software educativo</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -3269,7 +4091,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:37:11+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3299,12 +4125,30 @@
           <t>En el presente documento se muestra el desarrollo de una herramienta de software diseñada como apoyo en el proceso de enseñanza-aprendizaje del idioma inglés en el grado décimo de la Institución Educativa Gimnasio del Pacífico, (Tuluá- Valle); para estos se utilizó el Sistema de Gestión de Aprendizaje (LMS) Moodle que permitió el alojamiento y acceso a viarias actividades de aprendizaje, además de permitir la integración de plugin de tipo de preguntas, el manejo de gestión de usuarios, grupos, cursos y calificaciones generadas por la iteración de los estudiantes con las evaluaciones. Se crearon materiales educativos empaquetados (OVA) con el fin de usarlos en la plataforma de aprendizaje, bajo el estándar Scorm.</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>The project involves the development of a software tool to support English language learning in the 10th grade at Gimnasio del Pacífico, using Moodle as an LMS and creating OVA materials.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Objetos Virtuales de Aprendizaje (OVA), Sistema de Gestión de Aprendizaje (LMS)</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -3320,7 +4164,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:37:14+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3349,12 +4197,30 @@
           <t>El presente trabajo de grado consiste en el reconocimiento de las señas estáticas del abecedario del Lenguaje de Señas colombiano (LSC) con el fin de promover la inclusión social de las personas con diversidad funcional en el habla por medio de la tecnología. El proyecto se desarrolló bajo la metodología de Proceso Unificado Ágil (AUP), adoptando una arquitectura Modelo Vista Controlador (MVC) y un paradigma de programación orientado a objetos en la codificación. En su implementación se utilizan técnicas de procesamiento digital de imágenes para la segmentación, el mejoramiento de la imagen y proyección de contornos para la extracción de características. La clasificación de la seña se realiza por medio del algoritmo Dynamic Time Warping (DTW). Como resultado, el sistema logro reconocer en promedio el 79% de las señas estáticas con una desviación estándar del 6%.</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Natural language processing</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>The project involves the recognition of sign language symbols and their translation to written language, which is a form of natural language processing.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Lenguje de señas colombiano (LSC), Sistema de reconocimiento de señas</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>Procesamiento digital de imagenes</t>
@@ -3370,7 +4236,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:37:18+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3401,7 +4271,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>The project involves implementing a module for petitions, complaints, and claims within the 'ARQ Utilities' software development project for Arquitectsoft S.A.S., which suggests a management application for a specific organization.</t>
+          <t>The project involves implementing a module for petitions, complaints, and claims within the 'ARQ Utilities' software development project for Arquitectosoft S.A.S., which suggests it is a management application for a specific organization.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3426,7 +4296,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-04-25T17:41:25+00:00</t>
+          <t>2026-04-26T16:37:21+00:00</t>
         </is>
       </c>
     </row>
@@ -3456,12 +4326,30 @@
           <t>El presente trabajo de grado de Ingeniería de Sistemas en la Universidad del Valle sede Tuluá, tuvo como propósito identificar los activos de información de la empresa SOMEC S.A., así como también determinar las falencias en el actual manejo de estos, teniendo en cuenta que los activos de información son una parte muy importante en el funcionamiento idóneo de las organizaciones y empresas, su buen manejo genera una ventaja competitiva. Para dar cumplimiento a este objetivo se utilizó la metodología ágil XP (eXtreme Programming), apoyándose también en gerencia de procesos de negocio (BPM).</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="H58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>The project aims to develop a web-based system for managing business processes and information assets in the company SOMEC S.A, which is a typical example of an enterprise information system.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Activos de información, Gerencia de procesos de negocio (BPM)</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -3477,7 +4365,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:37:24+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3509,12 +4401,30 @@
           <t>En este trabajo de grado se implementó una aplicación web para la Institución Educativa Tulio Enrique Tascón de la ciudad de Buga con Objetos Virtuales de Aprendizaje (OVA) para la enseñanza de contenidos contables de los grados sexto y séptimo e implementar una extensión en el LMS Moodle para evaluación de los temas contables. Esta aplicación es un complemento teórico práctico, está compuesta y diseñada por diferentes actividades con el fin de dar apoyo a los profesores en la enseñanza de contenidos contables.</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>The project involves the development of a web application for educational purposes, specifically to support learning in accounting for grades six and seven at the Tulio Enrique Tascón institution. The use of Moodle as an LMS and OVA (Objetos Virtuales de Aprendizaje) suggests a focus on e-learning.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Aprendizaje virtual, Moodle (Plataforma de enseñanza-aprendizaje), Educación secundaria</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -3530,7 +4440,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:37:29+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3586,7 +4500,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-04-25T17:41:44+00:00</t>
+          <t>2026-04-26T16:37:31+00:00</t>
         </is>
       </c>
     </row>
@@ -3611,12 +4525,30 @@
           <t>El presente documento de trabajo de grado se describe el desarrollo una herramienta que incorpora OVA (Objetos Virtuales de Aprendizaje), para el apoyo a la enseñanza de la materia de Trigonometría de la Institución Educativa Leonor Lourido de Yumbo, Valle del Cauca; esta implementación involucró la investigación de un sistema de aprendizaje (LMS), que permite alojar y acceder libremente a los contenidos de las diversas actividades de aprendizaje. Esta herramienta es un complemento teórico práctico a los contenidos dictados en la Institución Educativa Leonor Lourido y se compone de definiciones teóricas con sus respectivos ejemplos, seguidos de actividades interactivas para los estudiantes, además de tareas asignadas para reforzar los conocimientos adquiridos.</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="H61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>The project involves the development of an OVA-based tool for teaching trigonometry, which is a key aspect of e-learning.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>OVA, Trigonometría, Enseñanza secundaria</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -3632,7 +4564,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:37:34+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3653,7 +4589,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3663,16 +4599,16 @@
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>The project aims to implement a system for managing software licenses, which is a common task in enterprise environments.</t>
+          <t>The project aims to manage software licenses for Carvajal S.A., a multinational company, by tracking the installed software and its corresponding purchase orders.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Licencia, Software, Riesgo legales, Organizaciones empresariales</t>
+          <t>licenciamiento, software, gestión de información</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3692,7 +4628,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-04-25T17:41:48+00:00</t>
+          <t>2026-04-26T16:37:37+00:00</t>
         </is>
       </c>
     </row>
@@ -3723,7 +4659,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3737,12 +4673,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>The project involves the development of a desktop application to manage access and usage of computer rooms at Universidad del Valle sede Tuluá, as well as the implementation of a plugin for GLPI system. This is a management application for a specific organization, which aligns with the definition of Enterprise information systems.</t>
+          <t>The project involves developing a desktop application for the University of Valle Sede Tuluá to manage access and usage of computer rooms, integrating with GLPI system.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Sistemas de acceso, Sistemas de control, Aplicaciones de escritorio</t>
+          <t>Sistemas de acceso, Sistemas de control</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3762,7 +4698,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-04-25T17:41:53+00:00</t>
+          <t>2026-04-26T16:37:40+00:00</t>
         </is>
       </c>
     </row>
@@ -3796,12 +4732,30 @@
           <t>El presente trabajo consiste en la evaluación de figuras acrobáticas que se usan en la creación de coreografías de baile. Tiene como objetivo principal, convertirse en una herramienta de apoyo para mujeres (docentes) que enseñan danzas, debido a que por su estructura física pueden versen limitadas en el momento en el que desee diseñar una coreografía que contenga alguna figura acrobática. El proyecto se desarrolló bajo la metodología de Proceso Unificado Ágil (AUP) adoptando una arquitectura Modelo, Vista, Controlador (MVC) junto al paradigma de programación orientado a objetos (POO). Para su implementación, se utiliza la tecnología del sensor Kinect que ayuda al reconocimiento del esqueleto y el movimiento de los usuarios. Además, se apoyó en el cálculo de ángulos que se forman en algunas partes del cuerpo, empleando el software GeoGebra para el cálculo de ángulos que se forman en algunas partes del cuerpo. Por último, para obtener una evaluación, se creó un algoritmo que extrae coordenadas tridimensionales correspondientes a unas articulaciones especificas del usuario, agrupándose por vectores, buscando con ello el cálculo y la comparación de cada uno de los ángulos formados y así proporcionarle al usuario conocer si la figura acrobática se está realizando de manera correcta.</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Information systems</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="H64" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>The project is a software tool designed to support women in creating dance coreographies with acrobatic figures, using computer technologies and sensors.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Danza, Baile, Coreografia</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>Procesamiento digital de imagenes</t>
@@ -3817,7 +4771,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:37:43+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3862,7 +4820,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>The project aims to implement a technological solution for project management in the company Proyectos - Mantenimiento Industrial M&amp;R, which is a classic example of an enterprise information system.</t>
+          <t>The project aims to implement a technological solution for project management in the company Proyectos - Mantenimiento Industrial M&amp;R, which suggests an enterprise-level application.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3887,7 +4845,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-04-25T17:41:56+00:00</t>
+          <t>2026-04-26T16:37:46+00:00</t>
         </is>
       </c>
     </row>
@@ -3920,10 +4878,14 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>The project title indicates the development of a web application for learning accounting and financial statements, which is a characteristic of e-learning artifacts.</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
+          <t>The project title indicates the development of a web application for educational purposes, specifically for learning accounting and financial statements for grades 6° and 8°.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>aprendizaje, contables, estados financieros</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>Objeto virtual de aprendizaje</t>
@@ -3941,7 +4903,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-04-25T17:41:59+00:00</t>
+          <t>2026-04-26T16:37:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3974,7 +4936,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>The project title mentions 'sistemas expertos' which implies a system that uses expertise to make decisions, but the focus is on comparing two such systems rather than their technical implementation or novelty.</t>
+          <t>The project title mentions 'sistemas expertos', which implies a type of information system, and the focus on veterinary disease diagnosis suggests a specific application but not a novel web or mobile product.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3999,7 +4961,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-04-25T17:42:02+00:00</t>
+          <t>2026-04-26T16:37:52+00:00</t>
         </is>
       </c>
     </row>
@@ -4044,12 +5006,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>The project involves creating a dataset and a web application to publish and link ecotourism information, which falls under the broader category of Information Systems.</t>
+          <t>The project involves creating a dataset and an application to link it with existing datasets on the Web of Data, which is a management task for a specific domain.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Turismo ecológico, Datos enlazados</t>
+          <t>Linked Open Data, Web de Datos</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4069,7 +5031,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-04-25T17:42:04+00:00</t>
+          <t>2026-04-26T16:37:55+00:00</t>
         </is>
       </c>
     </row>
@@ -4128,7 +5090,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-04-25T17:42:07+00:00</t>
+          <t>2026-04-26T16:37:58+00:00</t>
         </is>
       </c>
     </row>
@@ -4160,7 +5122,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4174,10 +5136,14 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>The project aims to develop a system for the CIAT's Genetic Area, which involves managing data and resources related to cassava research. The system will have features such as tracking, cost management, and reporting, which are typical of enterprise information systems.</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
+          <t>The project aims to develop a system for managing plant conservation and procedures in the Genética de Yuca area at CIAT, which involves structuring processes, resource management, and tracking genotypes and costs.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Sistemas de información Web, Banco de plantas in vitro, Genética de Yuca</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -4195,7 +5161,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-04-25T17:42:11+00:00</t>
+          <t>2026-04-26T16:38:02+00:00</t>
         </is>
       </c>
     </row>
@@ -4221,12 +5187,30 @@
 </t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="H71" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>The project aims to develop a system for managing the purchase and sale processes of Roger's establishment, which is focused on food production and sales. The system will also use data mining to support decision-making in purchasing ingredients and selling products.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sistemas de información, Compras, Gestión de compras, Administración de ventas</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -4242,7 +5226,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:38:06+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4269,12 +5257,30 @@
           <t>La empresa Nuevos Medios, tiene como producto una plataforma de aprendizaje en línea (elearning) llamada kme Lx (Knowledge Management Environment, Learning Experience) que le permite a sus clientes administrar su ambiente de aprendizaje, olvidando los obstáculos de espacio, tiempo y distancia, brindando la posibilidad de gestionar las capacitaciones e inducciones de sus empleados. De igual forma los cursos para que los estudiantes tengan acceso de manera virtual, haciéndoles un continuo seguimiento desde cualquier dispositivo, sean computador, tablet o smartphone. Debido a que el aprendizaje y el modo en que la persona adquiere conocimientos no tiene una forma definida como normalmente se piensa, la empresa Nuevos Medios con su plataforma de aprendizaje kme Lx, tomó la decisión de expandirse implementando el estándar LTI, (Learning tools interoperability) que permitirá a los administradores y tutores reutilizar contenidos que han creado otras personas, que viven en el ecosistema educativo virtual o e-learning y que está alojado en varios sitios por todo el internet, satisfacer las necesidades de sus usuarios. Si se reúne un conjunto de contenidos, que satisfacen necesidades específicas en un curso de kme Lx. El resultado será un curso con contenidos variados que hará la experiencia de aprendizaje más amena y de alta calidad para el estudiante y para el tutor o administrador. Con este módulo y bajo este estándar LTI, que facilita mucho la comunicación entre plataformas y herramientas externas, la plataforma kme Lx logrará ampliar y obtener una alta calidad en el proceso de formación del estudiante y que ayudará al tutor a crear sus cursos de manera fácil, rápida y económica, debido a que se va a reutilizar y adaptar los recursos disponibles que proveen estas herramientas de aprendizaje. Además de eso, se busca que la plataforma pueda proveer los cursos y contenidos que se han creado nativamente en ella y puedan utilizarse en otros ambientes de aprendizaje que lo requieran.</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="H72" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>The project involves the design and implementation of a module for integration with the Learning Tools Interoperability (LTI) standard in an e-learning platform, which is the central contribution.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>E-Learning, Ambientes virtuales de aprendizaje, Plataforma de aprendizaje</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -4290,7 +5296,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:38:09+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4323,7 +5333,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4337,12 +5347,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>The project developed a web-based tool to systematize the process of loading field books and data from an integrated system for the CIAT's bean program, which is a management application for a specific organization.</t>
+          <t>The project aims to develop a tool that helps systematize the process of loading field books and data from an integrated system for the CIAT's bean program, which is a management application for a specific organization.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Sistemas de información Web, Herramientas tecnológicas, Desarrollo de software</t>
+          <t>Sistemas de información Web, Aplicaciones Web</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4362,7 +5372,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-04-25T17:42:28+00:00</t>
+          <t>2026-04-26T16:38:13+00:00</t>
         </is>
       </c>
     </row>
@@ -4397,7 +5407,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4411,10 +5421,14 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>The project involves the development of a software application for a specific organization (IMEKT CLINIC) to manage its processes and provide a tool for its functioning.</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr"/>
+          <t>The project involves developing software modules for a specific company, IPSOFT S.A., to manage sales, contacts, and client appointments, which is a characteristic of Enterprise Information Systems.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Software de aplicación, Desarrollo de software</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -4432,7 +5446,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-04-25T17:42:34+00:00</t>
+          <t>2026-04-26T16:38:16+00:00</t>
         </is>
       </c>
     </row>
@@ -4486,7 +5500,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-04-25T17:42:37+00:00</t>
+          <t>2026-04-26T16:38:18+00:00</t>
         </is>
       </c>
     </row>
@@ -4519,7 +5533,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>The project involves developing a web application for managing processes, patient histories, and generating reports at the RYM IPS S.A.S. rehabilitation center, which is a specific organization.</t>
+          <t>The project involves developing a web application for managing processes, patient histories, and generating reports for a physical rehabilitation center, which is a specific organization.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4544,7 +5558,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-04-25T17:42:39+00:00</t>
+          <t>2026-04-26T16:38:21+00:00</t>
         </is>
       </c>
     </row>
@@ -4578,12 +5592,30 @@
           <t>El presente proyecto se basó en una problemática que se genera alrededor de la gestión de calificaciones de las instituciones educativas de Colombia, donde no se está evidenciando las falencias que tienen los estudiantes con respecto a los estándares de competencia dadas por el Ministerio de Educación Nacional. Para dar cumplimiento al problema propuesto se realizó el respectivo análisis, diseño y desarrollo de una aplicación web con modernas tecnologías para los procesos de competencia y estándares para determinar el rendimiento académico de los estudiantes, todo esto relacionado con la programación académica de la Institución. En la solución del proyecto , se basó en la metodología ICONIX y el uso de patrones arquitectónicos que plantea el Framework de Laravel, estableciendo un producto de alta calidad que desempeña las funcionalidades requeridas, ofreciendo los módulos más importantes para el planteamiento del problema como la gestión del año lectivo, la gestión académica, gestión de calificaciones y las más primordial la gestión de reportes donde se va evidenciar el rendimiento de cada estudiante por medio de los estándares de competencia</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="H77" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>The project is a management application for the Ministerio de Educación Nacional, with features such as gestion del año lectivo, gestión académica, and reportes academicos.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Enterprise information systems, Web applications</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -4599,7 +5631,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:38:24+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4629,7 +5665,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4643,12 +5679,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>The project is a management application for the Asoprovegas association in the rural area of Tuluá, which aims to improve the quality of life of its members by evaluating indicators of agroecological sustainability. The system, AGROIND, provides a work environment that meets the needs presented in the process of evaluation.</t>
+          <t>The project is a management application for the Asoprovegas-IAF association, implementing a system of information to register and analyze indicators of agroecological sustainability.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Sostenibilidad agroecológica, Asoprovegas, AGROIND</t>
+          <t>Sostenibilidad agroecológica, Sistemas de información</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4668,7 +5704,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-04-25T17:42:59+00:00</t>
+          <t>2026-04-26T16:38:27+00:00</t>
         </is>
       </c>
     </row>
@@ -4700,7 +5736,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4714,12 +5750,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>The project involves the development of functional capabilities for Cloud Defender and Cloud Insight products by Alert Logic Inc. Colombia, which is a company that provides security solutions in the cloud. The project was carried out as an internship program with the Universidad del Valle, where students were trained in the technologies used by the company.</t>
+          <t>The project involves developing features for Alert Logic Inc.'s products, which suggests a management application for the company.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Pasantía, Pruebas Unitarias, Defectos, AngularJS</t>
+          <t>Enterprise, information, systems</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4739,7 +5775,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-04-25T17:43:05+00:00</t>
+          <t>2026-04-26T16:38:30+00:00</t>
         </is>
       </c>
     </row>
@@ -4765,12 +5801,30 @@
 </t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>The project develops an application for the UMATA to support their processes and decision-making, which is a management application for a specific organization.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Aplicaciones Web, Bases de datos, Unidad Municipal de Asistencia Técnica Agropecuaria (UMATA), Usuarios, Toma de decisiones</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>Sistema de información</t>
@@ -4786,7 +5840,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:38:34+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4817,12 +5875,30 @@
           <t>En este proyecto, se hace una investigación acerca de los diferentes modelos emocionales para posteriormente relacionarlos con un modelo basado en el evolutivo tradicional. Todo esto, con el fin de implementar un prototipo que permita realizar simulaciones con Non-Player Character afectados por emociones, en aras de definir su relevancia a la hora de ser utilizadas en entornos de simulación de multitudes. A lo largo de este documento se presentan las distintas fases de su ejecución: Investigación, Implementación, Pruebas y Análisis. Así como los conceptos necesarios para su comprensión y las herramientas utilizadas para alcanzar los objetivos definidos. Por último, debido a la extensión del título proyecto, se hará referencia a sí mismo como el Proyecto SEA; donde SEA son las siglas para Ser Emocional Artificial, un nombre definido por su facilidad de pronunciación, poca extensión y pertinencia con las características y objetivos del proyecto.</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Artificial intelligence</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="H81" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>The project involves the development of a Non-Player Character (NPC) that uses emotions as a rule for artificial life in simulation environments, which is a central contribution to AI.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Non-Player Character, Computación emocional</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -4838,7 +5914,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:38:37+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4868,12 +5948,30 @@
           <t>La usabilidad de los sistemas interactivos es un atributo de calidad del software que posibilita a los usuarios realizar las tareas de forma fácil, intuitiva y cómoda, permitiendo alcanzar sus objetivos de manera rápida y satisfactoria. Paralelamente, la ausencia de herramientas para apoyar la evaluación de la usabilidad, específicamente evaluaciones heurísticas, se traduce en una desventaja para los evaluadores a la hora de llevar a cabo la verificación del grado de conformidad de un software en cuanto a un atributo importante como la usabilidad, así pues, la ausencia de dichas herramientas repercute en el tiempo empleado en la ejecución de la evaluación y a prescindir de aspectos importantes a la hora de analizar y realizar la respectiva conclusión. Con base en lo anterior, el aplicativo web expuesto en el presente documento se desarrolló en el marco de una investigación aplicada, la cual posibilitó por medio de la metodología de desarrollo Kanban, ofrecer a la comunidad una aplicación web que sirve de apoyo en el proceso de evaluación heurística, permitiendo a los evaluadores facilitar el proceso de análisis de los resultados y contribuir con trasmisión de conocimiento de manera oportuna.</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+      <c r="H82" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>The project is an application web that supports the evaluation of usability in interactive systems using multiple heuristic sets, which aligns with the definition of a web application.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Usabilidad, Evaluación heurística, Aplicaciones Web</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -4889,7 +5987,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:38:40+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4924,12 +6026,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mobile applications</t>
+          <t>Recommender systems</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -4938,10 +6040,14 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>The project involves designing and implementing an Android mobile application using techniques of artificial intelligence to provide recommendations for cyclists in the municipality of Tuluá.</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
+          <t>The project designs and implements a mobile app for Android devices using AI techniques to provide personalized recommendations to cyclists based on their daily shared data.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial, Aplicaciones móviles</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>Sistemas de recomendación</t>
@@ -4959,7 +6065,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-04-25T17:43:42+00:00</t>
+          <t>2026-04-26T16:38:43+00:00</t>
         </is>
       </c>
     </row>
@@ -4989,12 +6095,30 @@
           <t>En este proyecto se diseñó e implementó una aplicación web basada en la arquitectura (SOA). Una arquitectura que junto a la metodología de desarrollo SOMA, un hibrido entre la metodología RUP[13] y un enfoque basado en modelo de negocios, exigió un análisis tanto de los requerimientos de la aplicación, como del modelo de negocio de la fundación IPS FIME. En el análisis del modelo de negocio se identificaron políticas de la organización claves para establecer el alcance del proyecto y también, se clasificaron actividades en procesos de negocio con el fin de detectar los servicios a implementar. El siguiente paso, fue diseñar los servicios de acuerdo a los objetivos de la empresa, es decir a su modelo de negocio y políticas internas apoyándose en casos de usos y diagramas de Modelos y Notación de Procesos de Negocio (BPMN). Por otra parte, en la implementación se tomó como base la tecnología REST [12], una alternativa a SOAP [14] recomendado por W3C para aplicaciones robustas, la cual establece criterios para la comunicación entre servicios web empleando el protocolo HTTP. Una vez implementados los servicios en módulos de usuarios, pacientes, proveedores e historias clínicas, se integraron cada uno de estos módulos en una aplicación web desarrollada haciendo uso del framework Java Server Faces (JSF), el servidor de aplicaciones web GlassFish V4.0, el gestor de base de datos MySQL y la biblioteca de componentes PrimeFaces.</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="H84" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>The project involves designing and implementing a web application for the IPS FIME foundation, which includes user management, patient records, supplier management, and clinical history management. The system is based on SOA architecture and uses technologies such as REST, JSF, GlassFish, MySQL, and PrimeFaces.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Arquitectura Orientada a Servicios (SOA), Modelo de negocio, Administración de bases de datos, Sistemas de información Web</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>Desarrollo de software</t>
@@ -5010,7 +6134,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:38:48+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5075,7 +6203,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-04-25T17:43:45+00:00</t>
+          <t>2026-04-26T16:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -5108,12 +6236,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>The project title mentions 'BALANCED SCORECARD' which is a management tool, and the company name suggests it's for a specific organization.</t>
+          <t>The project title mentions a Balanced Scorecard adaptation for QualityColombia S.A., indicating it is an application for a specific company.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Balanced Scorecard, Enterprise information systems</t>
+          <t>Balanced Scorecard, QualityColombia S.A.</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5129,7 +6257,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-04-25T17:43:48+00:00</t>
+          <t>2026-04-26T16:38:54+00:00</t>
         </is>
       </c>
     </row>
@@ -5187,7 +6315,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-04-25T17:43:50+00:00</t>
+          <t>2026-04-26T16:38:57+00:00</t>
         </is>
       </c>
     </row>
@@ -5224,7 +6352,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5238,12 +6366,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>The project developed a mini-game called 'Fútbol Libre' to support physical therapy for patients with lower limb injuries, which is a serious game application.</t>
+          <t>The project involves developing a video game for physical therapy, with the goal of increasing patient motivation and engagement in rehabilitation. The game includes interactive elements and is designed to be used in a clinical setting.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Videogames, Physical Therapy, Playability, Player Experience, Heuristic Evaluation</t>
+          <t>Videojuegos, Terapia física, Rehabilitación física</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5263,7 +6391,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-04-25T17:43:55+00:00</t>
+          <t>2026-04-26T16:39:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5295,12 +6423,30 @@
           <t>El diagnóstico oportuno de una enfermedad es un proceso crítico, debido a que hay enfermedades de alto riesgo en las cuales un temprano diagnóstico es fundamental para evitar consecuencias irreversibles. Nuestro trabajo se enfoca en diseñar y probar estrategias para la categorización de la retinopatía diabética, a partir de información de imágenes procesadas de fondo de ojo con su respectivo diagnóstico. Esta enfermedad debe ser detectada en una etapa temprana, ya que de lo contrario el paciente presentará pérdida parcial o total de la visión, proceso gradual e irreversible. En diferentes estudios realizados se indica que el diagnóstico de un médico se ve afectado positivamente al estar apoyado de un sistema de decisión, lo que conlleva a una disminución de los exámenes realizados y así disminución de tiempo de espera. Para realizar la categorización de esta enfermedad, se utilizaron datos de imágenes de fondo de ojo procesadas, proporcionados por la base de datos Messidor y el proyecto An ensemble-based system for automatic screening of diabetic retinopathy . Así mismo, se realizó una exhaustiva revisión de literatura sobre algoritmos que se utilizan para el diagnóstico de la enfermedad, encontrando que los más relevantes son: Redes neuronales y Máquinas de Soporte Vectorial. Posteriormente, se llevó a cabo la implementación de tres algoritmos de inteligencia artificial para el diagnóstico de la enfermedad: Redes neuronales entrenadas con Backpropagation, Redes neuronales evolutivas y Máquina de soporte Vectorial. Al realizar un análisis comparativo de estos algoritmos, se encuentra que las redes neuronales entrenadas con Backpropagation son las que presentan mejores resultados en términos de precisión y tiempo de ejecución.</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Artificial intelligence</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="H89" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>The project focuses on designing and testing strategies for the categorization of diabetic retinopathy using artificial intelligence algorithms, specifically neural networks and support vector machines.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial, Algoritmos genéticos, Diagnóstico de enfermedades, Máquina de soporte vectorial, Redes neuronales</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>Inteligencia arificial</t>
@@ -5316,7 +6462,11 @@
           <t>llama3.1:8b</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>2026-04-26T16:39:10+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5346,7 +6496,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5360,10 +6510,14 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>The project involves the development of a videogame as a tool in the process of teaching English language for students, with mini-games and learning methodologies that combine entertainment and education.</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr"/>
+          <t>The project involves the development of a video game, EnglishPlay, as a tool for teaching English to engineering students. The game includes minigames and interactive elements that support learning objectives.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Videojuegos, Minijuegos, Enseñanza del inglés</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>Juegos serios</t>
@@ -5381,7 +6535,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-04-25T17:44:09+00:00</t>
+          <t>2026-04-26T16:39:13+00:00</t>
         </is>
       </c>
     </row>
@@ -5439,7 +6593,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-04-25T17:44:12+00:00</t>
+          <t>2026-04-26T16:39:16+00:00</t>
         </is>
       </c>
     </row>
@@ -5497,7 +6651,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-04-25T17:44:15+00:00</t>
+          <t>2026-04-26T16:39:19+00:00</t>
         </is>
       </c>
     </row>
@@ -5531,7 +6685,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5545,7 +6699,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>The project designs and develops a web application that integrates two techniques of recommendation: collaborative filtering and content-based recommendations, to suggest books to users in the Mario Carvajal library.</t>
+          <t>The project involves designing and developing a web application for book recommendations, integrating collaborative filtering and content-based recommendation techniques.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5570,7 +6724,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-04-25T17:44:20+00:00</t>
+          <t>2026-04-26T16:39:22+00:00</t>
         </is>
       </c>
     </row>
@@ -5603,12 +6757,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>The project involves developing a web application to manage processes and support decision-making for an optical point of sale, which suggests it is a management application for a specific organization.</t>
+          <t>The project title mentions a web application for managing processes and supporting decision-making, which suggests it is an enterprise-level system.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>web, application, management</t>
+          <t>web, gestionar, procesos</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5628,7 +6782,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-04-25T17:44:22+00:00</t>
+          <t>2026-04-26T16:39:25+00:00</t>
         </is>
       </c>
     </row>
@@ -5664,7 +6818,11 @@
           <t>The project title explicitly mentions a videogame as a tool for supporting the teaching and learning process in an academic subject, which aligns with the definition of serious games.</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr">
         <is>
           <t>Juegos serios</t>
@@ -5682,7 +6840,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-04-25T17:44:25+00:00</t>
+          <t>2026-04-26T16:39:27+00:00</t>
         </is>
       </c>
     </row>
@@ -5731,12 +6889,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>The project aims to create an educational videogame for teaching English to engineering students, using game mechanics and evaluation heuristics to improve usability and gameplay.</t>
+          <t>The project aims to create an educational videogame for teaching English to engineering students, using game mechanics and evaluation heuristics to improve learning outcomes.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Videojuegos, Minijuegos, Usabilidad</t>
+          <t>Videojuegos, Minijuegos</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5756,7 +6914,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-04-25T17:44:28+00:00</t>
+          <t>2026-04-26T16:39:30+00:00</t>
         </is>
       </c>
     </row>
@@ -5814,7 +6972,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-04-25T17:44:31+00:00</t>
+          <t>2026-04-26T16:39:34+00:00</t>
         </is>
       </c>
     </row>
@@ -5850,7 +7008,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>full_text</t>
+          <t>metadata_only</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5864,10 +7022,14 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>The project developed a video game, EnglishPlay, to support the teaching and learning of English in the Universidad del Valle sede Tuluá. The game includes challenges and retos that test the student's skills and motivate them to continue playing.</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
+          <t>The project involves developing a video game as a strategy to support the teaching of English I at Universidad del Valle Sede Tuluá, with the goal of improving student learning outcomes.</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Videojuegos, Minijuegos</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>Juegos serios</t>
@@ -5885,7 +7047,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-04-25T17:44:36+00:00</t>
+          <t>2026-04-26T16:39:37+00:00</t>
         </is>
       </c>
     </row>
@@ -5926,7 +7088,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>The project aims to develop an educational application to support virtual teaching and learning of English for students in the sixth grade at Institución Educativa María Antonia Ruiz, using OVAS (Objetos Virtuales de Aprendizaje) and tools like HTML5, CSS3, JAVASCRIPT, and MATERIALIZE.</t>
+          <t>The project aims to develop an educational application to support virtual teaching and learning of English for students in the sixth grade at María Antonia Ruiz Institution, using OVAS (Virtual Learning Objects) and web technologies such as HTML5, CSS3, JAVASCRIPT, and MATERIALIZE.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5951,7 +7113,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-04-25T17:44:40+00:00</t>
+          <t>2026-04-26T16:39:41+00:00</t>
         </is>
       </c>
     </row>
@@ -5992,7 +7154,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>The project involves the development of a web application for measuring competitiveness in the Center of Valle del Cauca, with features such as data storage and modification, which aligns with the characteristics of an Enterprise Information System.</t>
+          <t>The project involves the development of a web application for measuring competitiveness in the Center of the Cauca Valley, with features such as data storage and modification, which aligns with the characteristics of an Enterprise Information System.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6017,7 +7179,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-04-25T17:44:44+00:00</t>
+          <t>2026-04-26T16:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -6084,7 +7246,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-04-25T17:44:47+00:00</t>
+          <t>2026-04-26T16:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -6150,7 +7312,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-04-25T17:44:50+00:00</t>
+          <t>2026-04-26T16:39:51+00:00</t>
         </is>
       </c>
     </row>
@@ -6216,7 +7378,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-04-25T17:44:53+00:00</t>
+          <t>2026-04-26T16:39:54+00:00</t>
         </is>
       </c>
     </row>
@@ -6282,7 +7444,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-04-25T17:44:56+00:00</t>
+          <t>2026-04-26T16:39:57+00:00</t>
         </is>
       </c>
     </row>
@@ -6348,7 +7510,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:00+00:00</t>
+          <t>2026-04-26T16:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -6414,7 +7576,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:03+00:00</t>
+          <t>2026-04-26T16:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -6480,7 +7642,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:07+00:00</t>
+          <t>2026-04-26T16:40:08+00:00</t>
         </is>
       </c>
     </row>
@@ -6546,7 +7708,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:09+00:00</t>
+          <t>2026-04-26T16:40:11+00:00</t>
         </is>
       </c>
     </row>
@@ -6587,7 +7749,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>The project involves developing an adaptive hypermedia application to support the teaching of Physics, with interactive activities and content tailored to students' cognitive styles and needs.</t>
+          <t>The project involves developing an adaptive hypermedia application to support the teaching of Physics for students at a specific institution, using methodologies such as XP and METHADIS. The application includes interactive activities, historical and theoretical content, and assessments.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6612,7 +7774,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:13+00:00</t>
+          <t>2026-04-26T16:40:15+00:00</t>
         </is>
       </c>
     </row>
@@ -6678,7 +7840,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:16+00:00</t>
+          <t>2026-04-26T16:40:18+00:00</t>
         </is>
       </c>
     </row>
@@ -6724,7 +7886,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Recommender systems, Mobile applications</t>
+          <t>Recomendación de sitios turísticos, Aplicaciones móviles</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6744,7 +7906,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:19+00:00</t>
+          <t>2026-04-26T16:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -6777,12 +7939,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>The project title mentions a 'SISTEMA DE RECOMENDACION' which directly implies the use of recommender systems.</t>
+          <t>The project title mentions a 'SISTEMA DE RECOMENDACION' which directly implies the use of recommender systems, and there are no other keywords or abstract that contradict this classification.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>recomendacion, gestion, partidos, futbol, sala</t>
+          <t>recommender, systems</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6802,7 +7964,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:22+00:00</t>
+          <t>2026-04-26T16:40:24+00:00</t>
         </is>
       </c>
     </row>
@@ -6868,7 +8030,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:25+00:00</t>
+          <t>2026-04-26T16:40:27+00:00</t>
         </is>
       </c>
     </row>
@@ -6934,7 +8096,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:28+00:00</t>
+          <t>2026-04-26T16:40:30+00:00</t>
         </is>
       </c>
     </row>
@@ -6996,7 +8158,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:30+00:00</t>
+          <t>2026-04-26T16:40:33+00:00</t>
         </is>
       </c>
     </row>
@@ -7087,7 +8249,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:34+00:00</t>
+          <t>2026-04-26T16:40:36+00:00</t>
         </is>
       </c>
     </row>
@@ -7135,7 +8297,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>The project involves the development of a web application for measuring business competitiveness, with features such as data storage and management, user modification capabilities, and reporting tools.</t>
+          <t>The project involves the development of a web application for measuring competitiveness in the center of the Valle del Cauca, with features such as data storage and management, which are typical of enterprise information systems.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7156,7 +8318,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:37+00:00</t>
+          <t>2026-04-26T16:40:40+00:00</t>
         </is>
       </c>
     </row>
@@ -7227,7 +8389,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Lengua de Señas, Persona Sorda, Video</t>
+          <t>Lengua de Señas, Persona Sorda, Video, Inclusion</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7243,7 +8405,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:40+00:00</t>
+          <t>2026-04-26T16:40:43+00:00</t>
         </is>
       </c>
     </row>
@@ -7280,7 +8442,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>The project is a management application for a specific organization (SERVIGALO S.A.S), which suggests it falls under Enterprise Information Systems.</t>
+          <t>The project title mentions a web application for process management in a company, indicating it is an enterprise-level system.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7301,7 +8463,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:43+00:00</t>
+          <t>2026-04-26T16:40:46+00:00</t>
         </is>
       </c>
     </row>
@@ -7347,7 +8509,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>e-learning, adaptive hypermedia</t>
+          <t>e-learning, adaptive hypermedia, Physics</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7363,7 +8525,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:46+00:00</t>
+          <t>2026-04-26T16:40:49+00:00</t>
         </is>
       </c>
     </row>
@@ -7414,7 +8576,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>The project involves the design and development of an NPC adversary for a roguelike game using AI techniques, including neural networks to determine player type.</t>
+          <t>The project involves the design and development of an NPC adversario using techniques of artificial intelligence, including neural networks to determine player type.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7435,7 +8597,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:49+00:00</t>
+          <t>2026-04-26T16:40:52+00:00</t>
         </is>
       </c>
     </row>
@@ -7481,7 +8643,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>image, processing</t>
+          <t>retina, images, segmentation, classification</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7497,7 +8659,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:51+00:00</t>
+          <t>2026-04-26T16:40:55+00:00</t>
         </is>
       </c>
     </row>
@@ -7559,7 +8721,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>The project aims to develop an educational application to support virtual teaching and learning of English for sixth-grade students, using OVA's (Virtual Learning Objects) with tools like HTML5, CSS3, JAVASCRIPT, and MATERIALIZE.</t>
+          <t>The project aims to develop an educational application to support virtual teaching and learning of English for sixth-grade students, using OVA's (Objetos Virtuales de Aprendizaje) with tools like HTML5, CSS3, JAVASCRIPT, and MATERIALIZE.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7580,7 +8742,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:55+00:00</t>
+          <t>2026-04-26T16:40:58+00:00</t>
         </is>
       </c>
     </row>
@@ -7660,7 +8822,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-04-25T17:45:58+00:00</t>
+          <t>2026-04-26T16:41:01+00:00</t>
         </is>
       </c>
     </row>
@@ -7696,7 +8858,11 @@
           <t>The project title mentions 'gestión de procesos' and 'Administrativos', indicating a management application for an organization, which aligns with the definition of Enterprise Information Systems.</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr"/>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>procesos, administrativos</t>
+        </is>
+      </c>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
@@ -7710,7 +8876,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:00+00:00</t>
+          <t>2026-04-26T16:41:04+00:00</t>
         </is>
       </c>
     </row>
@@ -7769,7 +8935,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Procesamiento de lenguaje natural, terapia, lenguaje, android</t>
+          <t>Procesamiento de lenguaje natural, terapia, lenguaje</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -7785,7 +8951,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:04+00:00</t>
+          <t>2026-04-26T16:41:07+00:00</t>
         </is>
       </c>
     </row>
@@ -7844,7 +9010,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>The project involves the development of a web application for Quality Colombia S.A, which is an enterprise-level system that integrates various functions and provides control and management of activities.</t>
+          <t>The project involves the development of a web application for Quality Colombia S.A, which is an enterprise-level system that integrates various functions and provides control and management of activities to support business growth.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7865,7 +9031,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:07+00:00</t>
+          <t>2026-04-26T16:41:11+00:00</t>
         </is>
       </c>
     </row>
@@ -7917,7 +9083,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>The project aims to develop a mobile application with a recommendation system for tourists and commerce in the municipality of Ginebra, which suggests that the central contribution is indeed a recommender system.</t>
+          <t>The project aims to develop a mobile application with a recommendation system for tourists and commerce in Ginebra, allowing users to view available sites, rate them, and receive automated recommendations.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7938,7 +9104,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:10+00:00</t>
+          <t>2026-04-26T16:41:14+00:00</t>
         </is>
       </c>
     </row>
@@ -8012,7 +9178,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:13+00:00</t>
+          <t>2026-04-26T16:41:17+00:00</t>
         </is>
       </c>
     </row>
@@ -8080,7 +9246,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:17+00:00</t>
+          <t>2026-04-26T16:41:21+00:00</t>
         </is>
       </c>
     </row>
@@ -8165,7 +9331,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:20+00:00</t>
+          <t>2026-04-26T16:41:24+00:00</t>
         </is>
       </c>
     </row>
@@ -8217,7 +9383,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Information systems</t>
+          <t>Web applications</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -8226,7 +9392,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>The project develops a web-based tool for evaluating students' motivation, communication, and mathematical logic using fuzzy logic and the Takagi-Sugeno-Kang model. This is an information system that handles student evaluation data.</t>
+          <t>The project develops a web-based tool for evaluating students' motivation, communication, and mathematical logic using fuzzy logic and the Takagi-Sugeno-Kang model.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8247,7 +9413,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:24+00:00</t>
+          <t>2026-04-26T16:41:27+00:00</t>
         </is>
       </c>
     </row>
@@ -8319,7 +9485,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:27+00:00</t>
+          <t>2026-04-26T16:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -8381,7 +9547,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:29+00:00</t>
+          <t>2026-04-26T16:41:33+00:00</t>
         </is>
       </c>
     </row>
@@ -8427,7 +9593,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>E-learning, Gamificación</t>
+          <t>E-learning, gamificación</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8443,7 +9609,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:32+00:00</t>
+          <t>2026-04-26T16:41:36+00:00</t>
         </is>
       </c>
     </row>
@@ -8512,7 +9678,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:35+00:00</t>
+          <t>2026-04-26T16:41:39+00:00</t>
         </is>
       </c>
     </row>
@@ -8575,7 +9741,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:38+00:00</t>
+          <t>2026-04-26T16:41:42+00:00</t>
         </is>
       </c>
     </row>
@@ -8617,7 +9783,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>The project aims to develop a software that assists students in learning and understanding the concept of one-dimensional motion, which is a key aspect of physics education. The software is designed to support the appropriation of knowledge related to kinematics, indicating an educational artifact.</t>
+          <t>The project aims to develop a software that assists students in learning and understanding the concept of one-dimensional motion, which is a key aspect of physics education. The software is designed to support the appropriation of knowledge related to cinematics, indicating an educational artifact.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8638,7 +9804,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:43+00:00</t>
+          <t>2026-04-26T16:41:47+00:00</t>
         </is>
       </c>
     </row>
@@ -8679,7 +9845,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>The project involves the design and implementation of a web-based system for managing production data, which is a typical application of an enterprise information system.</t>
+          <t>The project involves the design and implementation of a web-based system for managing production data, which is a typical example of an enterprise information system.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8700,7 +9866,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:46+00:00</t>
+          <t>2026-04-26T16:41:50+00:00</t>
         </is>
       </c>
     </row>
@@ -8762,7 +9928,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:49+00:00</t>
+          <t>2026-04-26T16:41:54+00:00</t>
         </is>
       </c>
     </row>
@@ -8803,7 +9969,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>The project involves the development of a comprehensive management system for the Academic Secretary's office, which is a specific organization within the Universidad del Valle Sede Tuluá.</t>
+          <t>The project is a management application for the Secretariat of the Universidad del Valle Sede Tuluá, aiming to optimize and facilitate its processes.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8824,7 +9990,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:52+00:00</t>
+          <t>2026-04-26T16:41:57+00:00</t>
         </is>
       </c>
     </row>
@@ -8886,7 +10052,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:56+00:00</t>
+          <t>2026-04-26T16:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -8948,7 +10114,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-04-25T17:46:59+00:00</t>
+          <t>2026-04-26T16:42:03+00:00</t>
         </is>
       </c>
     </row>
@@ -9010,7 +10176,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:02+00:00</t>
+          <t>2026-04-26T16:42:06+00:00</t>
         </is>
       </c>
     </row>
@@ -9051,7 +10217,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>The project proposes the creation of a web application that translates subtitles from text to Colombian Sign Language (LSC), which is applied mainly to YouTube videos.</t>
+          <t>The project proposes the creation of a web application that translates subtitles from text to Colombian Sign Language (LSC), applied mainly to YouTube videos, which is a central contribution.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9072,7 +10238,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:05+00:00</t>
+          <t>2026-04-26T16:42:10+00:00</t>
         </is>
       </c>
     </row>
@@ -9122,7 +10288,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:07+00:00</t>
+          <t>2026-04-26T16:42:12+00:00</t>
         </is>
       </c>
     </row>
@@ -9163,7 +10329,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>The project integrates a model emotional and an evolutionary model based on agents to simulate the diffusion of knowledge between emotional agents in a virtual environment.</t>
+          <t>The project integrates a model emotional and an evolutionary model based on agents to simulate the diffusion of knowledge between emotional agents in a virtual environment type grid 2D, which is a characteristic of multi-agent systems.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9184,7 +10350,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:10+00:00</t>
+          <t>2026-04-26T16:42:16+00:00</t>
         </is>
       </c>
     </row>
@@ -9230,7 +10396,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>recomendación, entrenamientos, natación, IA, computación</t>
+          <t>recomendación, entrenamientos, natación, IA, computación, machine learning</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9246,7 +10412,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:14+00:00</t>
+          <t>2026-04-26T16:42:19+00:00</t>
         </is>
       </c>
     </row>
@@ -9287,12 +10453,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>The project is a management application for the Jardín Botánico Juan María Céspedes, which integrates techniques to effectively publish and link data on plant species, aligning with the Linked Open Data initiative.</t>
+          <t>The project is a management application for the Jardín Botánico Juan María Céspedes, which integrates techniques to effectively publish and link data on biological collections.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Linked, Open, Data</t>
+          <t>Linked Open Data, Colecciones Biologicas</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9308,7 +10474,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:17+00:00</t>
+          <t>2026-04-26T16:42:22+00:00</t>
         </is>
       </c>
     </row>
@@ -9370,7 +10536,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:20+00:00</t>
+          <t>2026-04-26T16:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -9411,12 +10577,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>The project involves analyzing sentiment and popularity of the Universidad del Valle during the student strike in 2018, which is a data mining task.</t>
+          <t>The project involves analyzing sentiment and popularity using data mining techniques to understand the impact of a student strike on the university's image.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Minería de datos, paro estudiantil</t>
+          <t>Minería de datos, paro estudiantil, análisis del sentimiento</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9432,7 +10598,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:23+00:00</t>
+          <t>2026-04-26T16:42:29+00:00</t>
         </is>
       </c>
     </row>
@@ -9478,7 +10644,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Sistema de Informacion, Extreme Programming</t>
+          <t>Sistema de Informacion, Emergencias</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9494,7 +10660,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:26+00:00</t>
+          <t>2026-04-26T16:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -9556,7 +10722,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:28+00:00</t>
+          <t>2026-04-26T16:42:35+00:00</t>
         </is>
       </c>
     </row>
@@ -9597,7 +10763,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>The project involves developing a vocational recommendation system to support students in choosing technical specialties at the Técnico Industrial Carlos Sarmiento Lora school, using AI and machine learning techniques.</t>
+          <t>The project title and abstract clearly indicate the development of a recommendation system for choosing technical specialties in a school, using AI and psychological models to segment user profiles.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9618,7 +10784,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:31+00:00</t>
+          <t>2026-04-26T16:42:38+00:00</t>
         </is>
       </c>
     </row>
@@ -9680,7 +10846,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:34+00:00</t>
+          <t>2026-04-26T16:42:40+00:00</t>
         </is>
       </c>
     </row>
@@ -9721,7 +10887,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>The project involves developing additional modules for the existing web application invessoft, which is used to manage events and research projects. The new modules aim to improve the functionality of the app and facilitate tasks such as user registration, evaluation, and budgeting.</t>
+          <t>The project involves developing additional modules for the Invessoft web application to improve its functionality and productivity, specifically for managing events, user registration, evaluations, dashboards, and budgets.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9742,7 +10908,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:38+00:00</t>
+          <t>2026-04-26T16:42:43+00:00</t>
         </is>
       </c>
     </row>
@@ -9783,7 +10949,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>The project's title and abstract clearly indicate the development of a recommendation system for geolocalized points of interest and tourist routes in Tuluá, using AI and Map Box.</t>
+          <t>The project title and abstract clearly indicate the development of a recommendation system for geolocalized points of interest and tourist routes in Tuluá, using AI and Map Box. The keywords also support this classification.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9804,7 +10970,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:41+00:00</t>
+          <t>2026-04-26T16:42:47+00:00</t>
         </is>
       </c>
     </row>
@@ -9866,7 +11032,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:44+00:00</t>
+          <t>2026-04-26T16:42:50+00:00</t>
         </is>
       </c>
     </row>
@@ -9928,7 +11094,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:46+00:00</t>
+          <t>2026-04-26T16:42:53+00:00</t>
         </is>
       </c>
     </row>
@@ -9970,7 +11136,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>The project aims to improve English technical skills in students through an interactive learning platform with gamification elements, such as lives, classification tables, rewards, and punishments.</t>
+          <t>The project aims to improve English technical skills in students through an interactive learning platform with gamification elements, such as lives, classification tables, rewards, and penalties.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9991,7 +11157,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:50+00:00</t>
+          <t>2026-04-26T16:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -10053,7 +11219,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:53+00:00</t>
+          <t>2026-04-26T16:43:00+00:00</t>
         </is>
       </c>
     </row>
@@ -10107,7 +11273,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:56+00:00</t>
+          <t>2026-04-26T16:43:02+00:00</t>
         </is>
       </c>
     </row>
@@ -10169,7 +11335,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-04-25T17:47:59+00:00</t>
+          <t>2026-04-26T16:43:06+00:00</t>
         </is>
       </c>
     </row>
@@ -10232,7 +11398,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:02+00:00</t>
+          <t>2026-04-26T16:43:09+00:00</t>
         </is>
       </c>
     </row>
@@ -10296,7 +11462,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:05+00:00</t>
+          <t>2026-04-26T16:43:12+00:00</t>
         </is>
       </c>
     </row>
@@ -10360,7 +11526,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:08+00:00</t>
+          <t>2026-04-26T16:43:15+00:00</t>
         </is>
       </c>
     </row>
@@ -10403,7 +11569,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>The project involves the maintenance of a software system for an educational institution, which suggests it is a management application for a specific organization.</t>
+          <t>The project aims to improve the efficiency of educational institutions by integrating administrative, teaching, and learning processes into a single system, which is a characteristic of Enterprise Information Systems.</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10424,7 +11590,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:10+00:00</t>
+          <t>2026-04-26T16:43:18+00:00</t>
         </is>
       </c>
     </row>
@@ -10465,7 +11631,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>The project aims to develop a web and mobile system for the Human Talent process in an agricultural technical institute, which involves managing administrative processes and storing data.</t>
+          <t>The project aims to develop a web and mobile system for the Human Talent process in an agricultural technical institute, which involves managing administrative processes and storing data related to personnel.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10486,7 +11652,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:14+00:00</t>
+          <t>2026-04-26T16:43:21+00:00</t>
         </is>
       </c>
     </row>
@@ -10549,7 +11715,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:16+00:00</t>
+          <t>2026-04-26T16:43:24+00:00</t>
         </is>
       </c>
     </row>
@@ -10611,7 +11777,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:20+00:00</t>
+          <t>2026-04-26T16:43:27+00:00</t>
         </is>
       </c>
     </row>
@@ -10654,12 +11820,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>The project aims to design and implement an online ordering system for restaurants, which will be accessed through a web application. The keywords 'Software', 'Application software', and 'System implementation' also support this classification.</t>
+          <t>The project aims to design and implement an online ordering system for restaurants, which will be delivered through a web application. The keywords 'Software', 'Application software', and 'System implementation' support this classification.</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>web, application, software</t>
+          <t>Web applications, Online ordering</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10675,7 +11841,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:23+00:00</t>
+          <t>2026-04-26T16:43:31+00:00</t>
         </is>
       </c>
     </row>
@@ -10737,7 +11903,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:26+00:00</t>
+          <t>2026-04-26T16:43:34+00:00</t>
         </is>
       </c>
     </row>
@@ -10799,7 +11965,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:29+00:00</t>
+          <t>2026-04-26T16:43:37+00:00</t>
         </is>
       </c>
     </row>
@@ -10845,7 +12011,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Preprocesamiento de datos, IA</t>
+          <t>Pandemia, Inmunidad de rebaño, Fake news, Preprocesamiento de datos, IA</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -10861,7 +12027,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:32+00:00</t>
+          <t>2026-04-26T16:43:40+00:00</t>
         </is>
       </c>
     </row>
@@ -10923,7 +12089,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:34+00:00</t>
+          <t>2026-04-26T16:43:43+00:00</t>
         </is>
       </c>
     </row>
@@ -10964,7 +12130,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>The project aims to develop an environment and an enemy NPC for a platformer game using AI techniques, which is a clear indication of a serious game development effort.</t>
+          <t>The project aims to develop an environment and an enemy NPC for a platform video game using AI techniques, which is a clear indication of a serious game development.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10985,7 +12151,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:38+00:00</t>
+          <t>2026-04-26T16:43:46+00:00</t>
         </is>
       </c>
     </row>
@@ -11026,7 +12192,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>The project involves the analysis of complex networks formed by student interactions in a programming course, using network science methods to study and characterize these relationships.</t>
+          <t>The project involves the analysis of complex networks formed by student interactions in a programming course, using network science methods to study and characterize these interactions.</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11047,7 +12213,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:40+00:00</t>
+          <t>2026-04-26T16:43:49+00:00</t>
         </is>
       </c>
     </row>
@@ -11088,7 +12254,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>The project aims to design an agent for predicting consumption patterns in postal services using AI, specifically neural networks.</t>
+          <t>The project aims to design an agent for predicting consumption patterns in postal services using artificial intelligence, specifically neural networks.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11109,7 +12275,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:43+00:00</t>
+          <t>2026-04-26T16:43:51+00:00</t>
         </is>
       </c>
     </row>
@@ -11150,7 +12316,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>The project aims to develop a web prototype that uses machine learning and adaptive learning to create a personalized learning path for students, which is a novel application of technology in education.</t>
+          <t>The project aims to develop a web prototype that uses machine learning and adaptive learning to determine the best learning style for each student and create a personalized learning path.</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11171,7 +12337,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:46+00:00</t>
+          <t>2026-04-26T16:43:54+00:00</t>
         </is>
       </c>
     </row>
@@ -11212,7 +12378,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>The project aims to implement gamified components in the AcademiAPP legacy application, leveraging technology to create engaging and motivating learning experiences for students.</t>
+          <t>The project aims to implement gamified components in the AcademiAPP, leveraging technology to create engaging and interactive learning experiences that motivate students.</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11233,7 +12399,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:49+00:00</t>
+          <t>2026-04-26T16:43:57+00:00</t>
         </is>
       </c>
     </row>
@@ -11274,7 +12440,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>The project involves designing and implementing a data pipeline for processing and transforming knowledge into a format suitable for training a model to extract relationships, which is a key aspect of information systems.</t>
+          <t>The project involves designing and implementing a data pipeline for processing and transforming knowledge into a format suitable for training a model for extracting relationships, which falls under the broader category of information systems.</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11295,7 +12461,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:52+00:00</t>
+          <t>2026-04-26T16:44:00+00:00</t>
         </is>
       </c>
     </row>
@@ -11357,7 +12523,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:55+00:00</t>
+          <t>2026-04-26T16:44:03+00:00</t>
         </is>
       </c>
     </row>
@@ -11398,12 +12564,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>The project involves the creation of a video game prototype to teach English to fifth-grade children, using emotional computing techniques. The game adjusts difficulty based on the player's emotions, which is a key aspect of serious games.</t>
+          <t>The project involves the creation of a video game prototype to teach English to fifth-grade children, using emotional computing techniques. The game adjusts difficulty based on the player's emotion, which is detected at the end of each level.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>videojuegos, algoritmos emocionales</t>
+          <t>videojuegos, computaci´on emocional</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11419,7 +12585,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-04-25T17:48:58+00:00</t>
+          <t>2026-04-26T16:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -11460,7 +12626,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>The project title and abstract clearly mention gamification elements, such as rewards, points, and levels of learning, to motivate officials in basic office training.</t>
+          <t>The project title and abstract clearly mention gamification elements, such as levels of learning, evaluations, points, and rewards, to motivate officials in the municipality of Tuluá.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11481,14 +12647,14 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:01+00:00</t>
+          <t>2026-04-26T16:44:09+00:00</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025S01</t>
+          <t>2024S01</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11543,14 +12709,14 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:04+00:00</t>
+          <t>2026-04-26T16:44:13+00:00</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025S02</t>
+          <t>2024S02</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11605,14 +12771,14 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:08+00:00</t>
+          <t>2026-04-26T16:44:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025S03</t>
+          <t>2024S03</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11651,7 +12817,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Control de inventario, sistema, software, sistemas de información</t>
+          <t>Control de inventario, sistema, software</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11667,14 +12833,14 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:11+00:00</t>
+          <t>2026-04-26T16:44:20+00:00</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025S04</t>
+          <t>2024S04</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11709,7 +12875,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>The project involves the development of a system to manage the production process of pimentón in an agricultural greenhouse, which is a typical example of an enterprise information system.</t>
+          <t>The project involves the development of a system to manage the administrative process of agricultural production of pimentón in an indoor greenhouse, which is a typical example of an enterprise information system.</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11730,14 +12896,14 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:14+00:00</t>
+          <t>2026-04-26T16:44:23+00:00</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025S05</t>
+          <t>2024S05</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11792,14 +12958,14 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:17+00:00</t>
+          <t>2026-04-26T16:44:26+00:00</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025S06</t>
+          <t>2024S06</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11858,14 +13024,14 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:21+00:00</t>
+          <t>2026-04-26T16:44:30+00:00</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025S07</t>
+          <t>2024S07</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11900,7 +13066,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>The project aims to develop a mobile application for students of Universidad del Valle sede Tuluá, which suggests that the primary delivery channel is a native or hybrid mobile app.</t>
+          <t>The project aims to develop a mobile application for students of Universidad del Valle sede Tuluá, which suggests that the primary contribution is a native or hybrid mobile app.</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11921,14 +13087,14 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:24+00:00</t>
+          <t>2026-04-26T16:44:33+00:00</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025S08</t>
+          <t>2024S08</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11963,7 +13129,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>The project involves updating the Sistema Administrador de Giros platform for CSI Consultores, which is a management application for a specific organization. The abstract mentions the importance of having an up-to-date system to support transactions and user access.</t>
+          <t>The project involves updating the Sistema Administrador de Giros (SAG) platform for CSI Consultores, which is a management application for a specific organization. The abstract mentions the importance of having an up-to-date information system to support organizational needs.</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11984,14 +13150,14 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:27+00:00</t>
+          <t>2026-04-26T16:44:37+00:00</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025S09</t>
+          <t>2024S09</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12047,14 +13213,14 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:30+00:00</t>
+          <t>2026-04-26T16:44:39+00:00</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025S10</t>
+          <t>2024S10</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12109,14 +13275,14 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:33+00:00</t>
+          <t>2026-04-26T16:44:42+00:00</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025S11</t>
+          <t>2024S11</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12150,7 +13316,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>The project aims to develop a tool using machine learning techniques to detect suicidal trends in Spanish texts, which involves natural language processing (NLP) methods.</t>
+          <t>The project aims to develop a tool using machine learning techniques to detect suicidal trends in Spanish texts, which involves text analysis and processing.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -12171,14 +13337,14 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:36+00:00</t>
+          <t>2026-04-26T16:44:46+00:00</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025S12</t>
+          <t>2024S12</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12233,14 +13399,14 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:39+00:00</t>
+          <t>2026-04-26T16:44:49+00:00</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025S13</t>
+          <t>2024S13</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12277,7 +13443,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>The project involves the implementation of a mobile app to support the adoption and reporting of lost pets in Tuluá, which aligns with the definition of a mobile application.</t>
+          <t>The project involves the implementation of a mobile app prototype to support the adoption and reporting of lost pets in Tuluá, which aligns with the definition of a mobile application.</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -12298,14 +13464,14 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:42+00:00</t>
+          <t>2026-04-26T16:44:52+00:00</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025S14</t>
+          <t>2024S14</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12339,7 +13505,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>The project aims to implement a web application and mobile app to systematize the company's processes, including inventory control and logistics management.</t>
+          <t>The project aims to implement a web application and mobile app to systematize the company's processes, including reception, storage, and manufacturing. This is a management application for a specific organization, which aligns with the definition of Enterprise information systems.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -12360,14 +13526,14 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:45+00:00</t>
+          <t>2026-04-26T16:44:56+00:00</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025S15</t>
+          <t>2024S15</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12393,7 +13559,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Serious games</t>
+          <t>Artificial intelligence</t>
         </is>
       </c>
       <c r="G199" t="inlineStr"/>
@@ -12402,12 +13568,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>The project involves the development of a system that generates music for video games, specifically RPGs, using machine learning techniques such as neural networks and genetic algorithms. The focus is on evaluating these techniques for their suitability in composing music for independent RPG games.</t>
+          <t>The project involves the implementation of two AI-based music generation techniques, Redes Neuronales Recurrentes and Algoritmos Genéticos, to compose music for RPG video games.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>M´usica, Videojuegos Independientes, Inteligencia Artificial</t>
+          <t>Inteligencia Artificial, M´usica Generativa</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12423,14 +13589,14 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:49+00:00</t>
+          <t>2026-04-26T16:44:59+00:00</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025S16</t>
+          <t>2024S16</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12485,14 +13651,14 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:52+00:00</t>
+          <t>2026-04-26T16:45:03+00:00</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025S17</t>
+          <t>2024S17</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12526,7 +13692,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>The project involves developing a matchmaking-based application to facilitate service acquisition for Univalle students, which suggests the use of recommender systems.</t>
+          <t>The project involves developing a matchmaking-based application to facilitate service acquisition for Univalle students, which suggests the use of recommender systems to match users with relevant services.</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -12547,14 +13713,14 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:55+00:00</t>
+          <t>2026-04-26T16:45:06+00:00</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025S18</t>
+          <t>2024S18</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12589,7 +13755,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>The project aims to develop and design architectures and infrastructure for the convergence of Cloud, TI, and TO technologies, which is a management application for an important company.</t>
+          <t>The project aims to develop and design architectures and infrastructure for the convergence of connectivity, Cloud, TI, and TO, which is a management application for a specific organization.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -12610,14 +13776,14 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-04-25T17:49:58+00:00</t>
+          <t>2026-04-26T16:45:09+00:00</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025S19</t>
+          <t>2024S19</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12651,7 +13817,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>The project proposes a mobile platform that uses a recommendation system to connect students seeking tutoring with suitable tutors, based on their specific needs and preferences.</t>
+          <t>The project aims to develop a mobile platform that uses a recommendation system to connect students seeking tutoring with suitable tutors, based on their specific needs and preferences.</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -12672,14 +13838,14 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:01+00:00</t>
+          <t>2026-04-26T16:45:12+00:00</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025S20</t>
+          <t>2024S20</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12734,14 +13900,14 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:04+00:00</t>
+          <t>2026-04-26T16:45:15+00:00</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025S21</t>
+          <t>2024S21</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12775,7 +13941,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>The project involves developing a web-based audio synthesizer using JavaScript and the Web Audio API, which is a novel contribution to the field of music education.</t>
+          <t>The project involves developing a web-based audio synthesizer using JavaScript and the Web Audio API, which is a central contribution to the field of web applications.</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -12796,14 +13962,14 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:07+00:00</t>
+          <t>2026-04-26T16:45:18+00:00</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025S22</t>
+          <t>2024S22</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12859,14 +14025,14 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:11+00:00</t>
+          <t>2026-04-26T16:45:22+00:00</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025S23</t>
+          <t>2024S23</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12923,14 +14089,14 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:15+00:00</t>
+          <t>2026-04-26T16:45:26+00:00</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025S24</t>
+          <t>2024S24</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12965,7 +14131,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>The project involves the development of a web application as a tool for supporting animal shelter recognition, with features such as interaction between shelters and the community.</t>
+          <t>The project involves the development of a web application as a tool to support animal shelter recognition, with features such as interaction between shelters and the community.</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -12986,14 +14152,14 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:18+00:00</t>
+          <t>2026-04-26T16:45:29+00:00</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025S25</t>
+          <t>2024S25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13027,7 +14193,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>The project aims to implement a system of information for DISCOTECA-BAR NIVELES CLUB, which is an enterprise-level application that will help the company manage its activities and reduce costs.</t>
+          <t>The project aims to implement a system of information for DISCOTECA-BAR NIVELES CLUB, which will help to streamline their activities and reduce time and costs. The system includes an application web and mobile that will allow employees to track product inventory and sales.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -13048,14 +14214,14 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:21+00:00</t>
+          <t>2026-04-26T16:45:33+00:00</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025S26</t>
+          <t>2024S26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13091,7 +14257,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>The project aims to develop a mobile application as support for the health and well-being of remote system engineers, which is a clear indication that the primary delivery channel is a native or hybrid mobile app.</t>
+          <t>The project aims to develop a mobile application as support for the health and well-being of remote-working systems engineers, which is a clear indication that the primary contribution is a mobile app.</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -13112,14 +14278,14 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:24+00:00</t>
+          <t>2026-04-26T16:45:36+00:00</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025S27</t>
+          <t>2024S27</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13176,14 +14342,14 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:28+00:00</t>
+          <t>2026-04-26T16:45:40+00:00</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025S28</t>
+          <t>2024S28</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13239,14 +14405,14 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:31+00:00</t>
+          <t>2026-04-26T16:45:43+00:00</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025S29</t>
+          <t>2024S29</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13303,14 +14469,14 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:34+00:00</t>
+          <t>2026-04-26T16:45:46+00:00</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025S30</t>
+          <t>2024S30</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13344,12 +14510,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>The project aims to develop a platform for electoral statistical control, which will provide relevant and precise information on electoral data at the departmental and municipal levels in Valle del Cauca. This platform is intended to improve decision-making efficiency by providing accurate information to political actors.</t>
+          <t>The project aims to develop a platform for electoral statistical control, which will provide relevant and precise information on voting data, election results, and voter behavior. This platform is designed to improve decision-making efficiency for political actors, making it an enterprise information system.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Sistemas de información, TIC, Estadísticas electorales</t>
+          <t>Sistemas de información, Estadísticas electorales</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13365,14 +14531,14 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:38+00:00</t>
+          <t>2026-04-26T16:45:49+00:00</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025S31</t>
+          <t>2024S31</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13406,12 +14572,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>The project aims to develop a game for learning programming concepts, and the evaluation is in terms of learning outcomes.</t>
+          <t>The project aims to develop a game for supporting learning in the 'Fundamentos de Programaci´on Imperativa' course, using gamification and interactive elements to motivate students.</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Videojuegos, juego serio</t>
+          <t>Videojuegos, juego serio, pensamiento computacional, gamificacion</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13427,14 +14593,14 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:40+00:00</t>
+          <t>2026-04-26T16:45:53+00:00</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025S32</t>
+          <t>2024S32</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13473,7 +14639,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>IA (Inteligencia artificial), Computaci´on afectiva</t>
+          <t>Inteligencia artificial, Computaci´on afectiva</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -13489,14 +14655,14 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:44+00:00</t>
+          <t>2026-04-26T16:45:56+00:00</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025S33</t>
+          <t>2024S33</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13551,14 +14717,14 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:46+00:00</t>
+          <t>2026-04-26T16:45:59+00:00</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025S34</t>
+          <t>2024S34</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13595,7 +14761,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>The project involves the migration and redesign of an existing system to a more modular architecture, which is a software engineering task.</t>
+          <t>The project involves the migration and redesign of an existing system to a decoupled architecture, which is a software engineering task.</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -13616,14 +14782,14 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:50+00:00</t>
+          <t>2026-04-26T16:46:02+00:00</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025S35</t>
+          <t>2024S35</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13678,14 +14844,14 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:52+00:00</t>
+          <t>2026-04-26T16:46:05+00:00</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025S36</t>
+          <t>2024S36</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13740,14 +14906,14 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:55+00:00</t>
+          <t>2026-04-26T16:46:07+00:00</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025S37</t>
+          <t>2024S37</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13786,7 +14952,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Aplicación web, prototipo, interaccion, redes sociales</t>
+          <t>Aplicación web, prototipo</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -13802,14 +14968,14 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>2026-04-25T17:50:58+00:00</t>
+          <t>2026-04-26T16:46:10+00:00</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025S38</t>
+          <t>2024S38</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13844,7 +15010,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>The project involves the development of additional modules for AcademiApp, a software application used by Universidad del Valle sede Tuluá, to address specific problems in an academic and administrative context.</t>
+          <t>The project involves the development of additional modules for AcademiApp, a software application used by an educational institution, to address specific administrative and academic needs.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -13865,14 +15031,14 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>2026-04-25T17:51:02+00:00</t>
+          <t>2026-04-26T16:46:14+00:00</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025S39</t>
+          <t>2024S39</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -13906,7 +15072,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>The project proposes the creation and implementation of a software audit prototype for protecting information in Windows 11, addressing security needs and international standards.</t>
+          <t>The project proposes the creation and implementation of a software audit prototype for protecting information in Windows 11, which is a key aspect of cybersecurity.</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -13927,14 +15093,14 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>2026-04-25T17:51:05+00:00</t>
+          <t>2026-04-26T16:46:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025S40</t>
+          <t>2024S40</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -13968,7 +15134,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>The project aims to develop a mobile application for food delivery, using the Flutter SDK and SCRUM methodology.</t>
+          <t>The project aims to develop a mobile application for food delivery, using Flutter SDK and SCRUM methodology.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -13989,14 +15155,14 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>2026-04-25T17:51:07+00:00</t>
+          <t>2026-04-26T16:46:19+00:00</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025S41</t>
+          <t>2024S41</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14030,7 +15196,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>The project aims to develop a web tool for managing information in beauty salons, which is a specific industry with its own set of services and challenges. The system will help salons adapt to changing demands and improve their financial health.</t>
+          <t>The project aims to develop a web tool for managing information in beauty salons, which is a specific industry with its own set of services and challenges. The focus on management and control of resources, customer relationships, and service history aligns with the characteristics of enterprise information systems.</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -14051,14 +15217,14 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>2026-04-25T17:51:11+00:00</t>
+          <t>2026-04-26T16:46:23+00:00</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025S42</t>
+          <t>2024S42</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14086,11 +15252,7 @@
           <t>Web applications</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Recommender systems</t>
-        </is>
-      </c>
+      <c r="G226" t="inlineStr"/>
       <c r="H226" t="n">
         <v>0.9</v>
       </c>
@@ -14101,7 +15263,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Sistema de Recomendaci´on, Filtrado Colaborativo</t>
+          <t>Sistema de Recomendaci´on, Filtrado Colaborativo, Aplicaci´on Web</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14117,14 +15279,14 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>2026-04-25T17:51:14+00:00</t>
+          <t>2026-04-26T16:46:27+00:00</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025S43</t>
+          <t>2024S43</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14168,7 +15330,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>The project aims to develop a web-based system for recommending motorcycle purchases, leveraging AI and digitalization to suggest products based on user preferences.</t>
+          <t>The project aims to develop a web-based system for recommending motorcycle purchases, leveraging AI and digitalization to suggest motorcycles that match users' needs.</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -14189,14 +15351,14 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>2026-04-25T17:51:17+00:00</t>
+          <t>2026-04-26T16:46:30+00:00</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025S44</t>
+          <t>2024S44</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14230,12 +15392,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>The project aims to develop an e-commerce application for Family Pizza, a company in Tuluá, which suggests it is a management application for a specific organization.</t>
+          <t>The project aims to develop an e-commerce application for Family Pizza, which is a company-based system with specific business goals and objectives.</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>E-commerce, Negocios</t>
+          <t>E-commerce, Empresas virtuales</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -14251,7 +15413,1313 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>2026-04-25T17:51:20+00:00</t>
+          <t>2026-04-26T16:46:33+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2025S01</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>SISTEMA DE IDENTIFICACION DE INSTRUMENTOS MUSICALES DE LA REGION ANDINA USANDO TECNICAS DE MACHINE LEARNING</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Identificador, Intrumentos musicales, Musica andina, Inteligencia Artificial, Machine Learning</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Este proyecto presenta el desarrollo de un sistema de identificación de instrumentos musicales específicos de la región andina utilizando diferentes técnicas de Machine Learning. El sistema propuesto emplea algoritmos de clasificación para analizar y categorizar sonidos musicales, facilitando la identificación automática de instrumentos como la quena, el charango, la zampoña y el bombo andino, entre otros adicionales. Se recolectarán datos acústicos de diversas fuentes y se procesarán para extraer características relevantes que alimenten los modelos de aprendizaje automático.</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Machine learning</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a system that uses machine learning techniques to identify specific musical instruments from the Andean region, indicating that machine learning is the central contribution.</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Machine Learning, Inteligencia Artificial</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:33:47+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2025S02</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SISTEMA EN GESTION INTEGRAL DE FACTURACIÓN DIGITAL PARA PEQUENOS PRESTADORES DE SERVICIOS PÚBLICOS</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Sistema de facturación, Servicios públicos, Prototipo wireframes, Prototipo mockups</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Este documento describe la implementación de un sistema de facturación digital para pequeños prestadores de servicios públicos, específicamente en el contexto de acueductos de pequeña escala. La necesidad de optimizar y automatizar este proceso se debe a las limitaciones y deficiencias actuales en la gestión financiera de estos sistemas, que afectan la precisión, eficiencia y transparencia en la administración de los mismos. El objetivo del prototipo logrado es proporcionar un sistema de facturación digital adaptado a las particularidades y necesidades específicas de las pequeñas entidades que prestan servicios públicos. El prototipo proporciona funcionalidades clave para agilizar la generación de facturas, facilitar la gestión de usuarios y mejorar la transparencia en la administración financiera, permitiendo obtener datos específicos que pue den servir como base de datos informativa para la entidad. La creación del prototipo se realizó mediante un enfoque ágil, utilizando instrumentos y tecnologías actuales para el diseño y desarrollo del sistema. Se desarrollaron wireframes y mockups que permitieron dar una percepción clara del sistema al usuario final. El prototipo fue sometido a pruebas que confirmaron su funcionalidad y eficiencia en el procesamiento de datos y carga masiva de información. Los resultados obtenidos muestran que el prototipo tiene una buena aceptación y su procesamiento es eficiente. Se espera que el sistema desarrollado contribuya significativamente a la mejora de la gestión financiera en pequeños acueductos, ofreciendo una solución integral y adaptada a las necesidades de la entidad que lo desee implementar. La implementación de este sistema puede tener un impacto positivo en la eficiencia y transparencia de la gestión financiera de estos sistemas.</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>The project aims to develop a digital facturation system for small public service providers, with specific functionalities to improve financial management and transparency.</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Sistema de facturación, Servicios públicos</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:33:50+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2025S03</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>SISTEMATIZACIÓN DE LA GESTIÓN ADMINISTRATIVA DE INFORMACIÓN Y LÓGICA DE NEGOCIO PARA LA RECOLECCIÓN DE DESECHOS EN LA EMPRESA AGUAS DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Desarrollo de software, sistematización, gestión administrativa, operación de negocios</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>En este documento se aborda la profundización respecto a la necesidad de un sistema integral alrededor del gestionamiento y la administración de la información de las operaciones de negocio en la empresa Aguas de la Sabana de Bogotá S.A E.S.P., una empresa privada prestadora de los servicios de acueducto, alcantarillado y aseo, que contribuye al desarrollo de los municipios de Cota, Funza y Tenjo. El objetivo es mejorar la administración de acuerdos y tarifas según norma CRA 151 del 2001, Anexo 8, la gestión de clientes y técnicos/operarios registrados, la relación de información de rutas, micro rutas y clientes correspondientes a las mismas, y la gestión de los recursos operacionales como los camiones de recolección, entre otros. Contribuyendo así a la mejora de la experiencia tanto del administrador como de los operarios y al cumplimiento normativo de la empresa.</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>The project aims to develop a system for the administrative management of information and business logic for waste collection in Aguas de la Sabana, which is a company that provides water, sewage, and sanitation services. The keywords 'Desarrollo de software', 'sistematización', and 'gestión administrativa' indicate that this project involves developing an enterprise-level system.</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Enterprise information systems, software development, systematization, administrative management</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:33:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2025S04</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PROTOTIPO DE SISTEMA DE RECOMENDACIÓN PARA ELECCIÓN DE VEHÍCULO TIPO MOTOCICLETA BASADO EN FILTRADO COLABORATIVO</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Inteligencia Artificial, Sistemas de recomendación, Filtrado Colaborativo, Características específicas, Motocicletas</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>La elección de una motocicleta es un proceso complejo que puede resultar abrumador para los usuarios debido a la diversidad de opciones disponibles y las diferentes necesidades y preferencias individuales. La propuesta de un sistema de recomendación de motocicletas buscó abordar este desafío al proporcionar orientación personalizada y precisa a los usuarios en su búsqueda del vehículo perfecto. Este sistema se implementó utilizando una metodología basada en el análisis de datos, el aprendizaje automático y el filtrado colaborativo. A través de estas tecnologías, se comprendieron las preferencias de los usuarios y se sugirieron motocicletas que se adaptaran mejor a sus necesidades y gustos individuales. De esta manera, el sistema ofreció recomendaciones personalizadas que se alinearon específicamente con las características y preferencias únicas de cada usuario, mejorando significativamente la precisión y relevancia de las sugerencias. Los resultados obtenidos mostraron una mejora considerable en la satisfacción del usuario al reducir el tiempo y esfuerzo necesarios para encontrar una motocicleta adecuada, adaptándose de forma precisa a las necesidades personales de cada individuo.</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Recommender systems</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a system of recommendation for choosing a type of motorcycle based on collaborative filtering, which is the central contribution.</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Recommender, Collaborative</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:33:57+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2025S05</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>PRONUNCIAPP: PROTOTIPO DE APLICACION WEB PARA LA MEJORA DE LA PRONUNCIACIÓN DEL INGLÉS EN LOS ESTUDIANTES DE LA CARRERA DE INGENIERÍA DE SISTEMAS DE LA UNIVERSIDAD DEL VALLE, SEDE TULUÁ</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Prototipo aplicación web, inteligencia artificial, idioma ingles, PronunciApp</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>PronunciApp es un prototipo de aplicación web desarrollado como proyecto de grado para proporcionar una mejora sobre la pronunciación del idioma inglés a estudiantes de Ingeniería de Sistemas de la Universidad del Valle, sede Tuluá. El sistema implementado permite a los usuarios grabar su voz al repetir palabras en inglés, las cuales son analizadas utilizando tecnologías de reconocimiento de voz para generar retroalimentación sobre aspectos de la pronunciación. La aplicación se desarrolló utilizando Angular 19 para la interfaz de usuario, FastAPI para el backend, y se desplegó en la plataforma Azure. El proceso de desarrollo siguió la metodología Scrumban a lo largo de 40 sprints, aplicando principios de diseño UX/UI para crear una herramienta que permite la práctica de pronunciación mediante el análisis de grabaciones de audio.</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>The project is a web application designed to improve English pronunciation in students, utilizing technologies such as voice recognition and analysis.</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>web, application, pronunciation</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:00+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2025S06</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CREACIÓN DE MÓDULOS INTERACTIVOS PARA EL DESARROLLO CONTINUO DE LA ORATORIA Y EL PENSAMIENTO CRÍTICO DE TEXTOS EN EL PROTOTIPO DE ENSEÑANZA DE HABILIDADES BLANDAS</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Procesamiento del lenguaje natural, Comunicación efectiva, pensamiento crítico, plataforma educativa, habilidades blandas, inteligencia artificial.</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Con frecuencia, se observa que la importancia de ciertas habilidades es pasada por alto en los programas de formación, a pesar de su relevancia en el mercado laboral actual y futuro. La comunicación efectiva y el pensamiento crítico constituyen pilares importantes para que los ingenieros puedan abordar los desafíos venideros y ofrecer soluciones de calidad a sus clientes. El descuido de estas habilidades en la formación de ingenieros puede ocasionar consecuencias negativas tanto en su desempeño profesional como en el éxito de los proyectos que emprendan. Este proyecto se centró en crear y poner en marcha módulos interactivos para el desarrollo de habilidades de oratoria y pensamiento crítico dirigidos específicamente a los estudiantes de ingeniería de sistemas de la Universidad del Valle en Tuluá. Se implementaron estrategias educativas que incluyen el uso de inteligencia artificial y procesamiento de lenguaje natural para proporcionar retroalimentación personalizada a los estudiantes. Al impulsar el desarrollo de estas habilidades, las instituciones educativas pudieron contribuir de manera significativa a la formación de profesionales versátiles y capacitados que estuvieran mejor preparados para enfrentar los desafíos venideros con mayor confianza y competencia.</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>E-learning</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>The project focuses on creating interactive modules for the development of soft skills, specifically oratory and critical thinking, using AI and NLP strategies in an educational platform.</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Procesamiento del lenguaje natural, Comunicación efectiva</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:03+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2025S07</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN SOFTWARE PARA LA PREDICCIÓN DE VENTAS FUTURAS UTILIZANDO MODELOS PREDICTIVOS.</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Aplicativo web, pronostico en ventas, futuras, modelos predictivos, inteligencia artificial, PYMES</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>En este trabajo de grado se aborda el desarrollo de un aplicativo de software para el pronóstico de ventas utilizando algoritmos de inteligencia artificial. El problema evidenciado es la carencia de una herramienta que permita a las pequeñas y medianas empresas (PYMES) tomar mejores decisiones de manera informada para la gestión de su inventario ya que para una empresa tener una buena gestión del inventario es crucial ya que las ventas pueden fluctuar de una manera poco predecible lo que puede llevar a pérdidas eco nómicas por tener poco o demasiado inventario. Las pequeñas empresas, pueden enfrentar más dificultades en la gestión del inventario, lo cual puede resultar poco eficiente debido a que suelen realizar esta gestión de manera manual y sin un estudio previo. El objetivo principal de este trabajo de grado es crear una herramienta capaz de generar pronósticos de ventas precisos a partir de datos históricos, integrando modelos predicti vos entrenados con técnicas de machine learning. Para ello, se implementaron y evaluaron tres modelos distintos: una red neuronal LSTM (Long Short-Term Memory), un modelo de soporte vectorial para regresión (SVM) con distintos kernels, y un modelo estadístico SARIMA (Seasonal Autoregressive Integrated Moving Average). Las métricas utilizadas para evaluar el desempeño de los modelos fueron el Error Cuadrático Medio (MSE), el Error Absoluto Medio (MAE) y el Error Porcentual Absoluto Medio (MAPE). El proyecto fue desarrollado bajo la metodología ágil Scrum, adaptada para un entorno de trabajo individual</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>The project involves developing a software application for predicting future sales using predictive models, which is delivered through a web interface.</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Aplicativo web, pronostico en ventas</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:06+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2025S08</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE APLICACIÓN WEB COMO HERRAMIENTA DE APOYO PARA LA EVALUACIÓN DE COMPETENCIAS EN PENSAMIENTO COMPUTACIONAL</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Metodologías educativas, pensamiento computacional, evaluación de competencias, aplicación web</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>El pensamiento computacional se ha consolidado como una habilidad fundamental para el siglo XXI, ya que permite a los individuos comprender y participar activamente en el mundo digital. En el caso de los jóvenes, su desarrollo aporta beneficios significativos en múltiples dimensiones. En primer lugar, promueve el razonamiento lógico y el pensamiento crítico, al requerir que los estudiantes aborden problemas de manera sistemática y estructurada, estas habilidades resultan clave tanto para el desempeño académico como para la toma de decisiones en la vida cotidiana. Además, estimula la creatividad y la innovación, al incentivar la búsqueda de soluciones originales a diversos retos, capacidades especialmente valoradas en el contexto actual. Asimismo, el pensamiento computacional prepara a los jóvenes para enfrentar los desafíos del mercado laboral, especialmente en áreas relacionadas con la ciencia, la tecnología, la ingeniería y las matemáticas, donde estas competencias son cada vez más demandadas. Reconociendo su relevancia, se han propuesto múltiples metodologías para enseñar pensamiento computacional, cada una con distintos enfoques y estrategias de evaluación. Sin embargo, las investigaciones evidencian deficiencias en los métodos de evaluación existentes, lo que dificulta validar de forma efectiva el aprendizaje de estas competencias. Ante esta problemática, el presente trabajo propone el desarrollo de una aplicación web parametrizable, orientada a evaluar las competencias en pensamiento computacional de estudiantes de educación secundaria. La solución se fundamentará en un modelo de evaluación integral que combine enfoques formales e informales, haciendo uso de rúbricas para valorar el desempeño de los estudiantes en tareas específicas relacionadas con el pensamiento computacional.</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>The project proposes the development of a web application to evaluate students' competencies in computational thinking, which is a novel contribution in the field of educational technology.</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>aplicación, web</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2025S09</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE PRUEBAS UNITARIAS PARA EL COMPONENTE FRONT-END DEL SOFTWARE ACADEMIAPP PARA LA EMPRESA WEBCLOSTER SAS</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Desarrollo de software Scrum, pruebas unitarias, gestión acádemica, gestión administrativa, AcademiApp</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Cada vez es más crucial para las universidades sistematizar la gestión tanto administrativa como académica. Varias compañías de software han identificado esta necesidad y han entrado en este mercado, entre ellas Webcloster S.A.S. Webcloster S.A.S. es una empresa que se dedica al desarrollo de software que simplifica la dirección y administración de operaciones tanto empresariales como personales, y ha decidido crear un programa llamado AcademiApp para la gestión académica y administrativa. Este programa consiste en una aplicación en línea que facilita la administración de datos, la consulta de horarios disponibles de las aulas, la evaluación de desempeños, entre otras funciones. Para este proyecto se empleará una metodología de investigación aplicada y, adicionalmente, se utilizará la metodología ágil Scrum. Con lo mencionado anteriormente, se espera desarrollar pruebas y realizar el mantenimiento de los módulos asignados para AcademiApp.</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>The project involves developing a software application, AcademiApp, for the company Webcloster SAS to manage academic and administrative tasks, which falls under Enterprise Information Systems.</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>pruebas unitarias, gestión acádemica, gestión administrativa</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:12+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2025S10</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>PROTOTIPO WEB COMO SOPORTE PARA LA ENSEÑANZA DE INGLÉS A TRAVÉS DE LA GAMIFICACIÓN Y ALGORITMOS DE PROCESAMIENTO DEL LENGUAJE NATURAL</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Lenguaje natural, gamificación, aprendizaje, habla en ingles, inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>El presente proyecto desarrolló un prototipo web diseñado para mejorar la habilidad del habla en inglés mediante el uso de técnicas de Procesamiento del Lenguaje Natural (PLN) y gamificación. Se aborda la creciente necesidad de herramientas educativas efectivas que involucren a los estudiantes de manera activa y atractiva. El sistema proporciona ejercicios interactivos y elementos de gamificación para motivar a los usuarios a practicar y mejorar su comprensión al momento de hablar en inglés. El enfoque que tiene el sistema aporta al estudiante una herramienta con IA centralizada en distintos algoritmos de PLN con el fin de que el estudiante obtenga un apoyo en el proceso de aprendizaje y que, con ayuda de estos modelos matemáticos, pueda mejorar su fluidez al momento de comunicarse en inglés.</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Gamification</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>The project title and abstract clearly indicate the use of gamification as a primary object of study to support English language learning.</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>gamificación, aprendizaje</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:15+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2025S11</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SOFTWARE WEB PARA EL ANÁLISIS Y EVALUACIÓN DE LA EXPOSICIÓN DE DATOS SENSIBLES Y NO SENSIBLES EN LA RED SOCIAL INSTAGRAM APLICADA EN LA UNIVERSIDAD DEL VALLE SEDE TULUÁ</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Procesamiento de Lenguaje Natural, Web Scraping, campus universitario, privacidad de datos, redes sociales.</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>En esta propuesta de trabajo de grado se busca la implementación de un prototipo de software web para capturar la información de texto de las redes sociales (web Scraping o API web scraper) y poder identificar el nivel de exposición de los datos personales sensibles y no sensibles en los campus universitarios, con este proyecto, se quiere motivar a otras entidades educativas a adoptar un enfoque similar, donde el factor clave es promover una cultura ge neral de privacidad y seguridad en línea en todas las comunidades universitarias. Asimismo, se espera formar un futuro digital donde la protección de datos personales sea uno de los pi lares fundamentales, garantizando así un mejor ambiente universitario tanto confiable como respetuoso para todos los miembros que la componen. El presente proyecto constituye una posibilidad hacia la creación de entornos universita rios más seguros y respetuosos de la privacidad. Destacando el papel crucial que la tecnología desempeña como aliada en la protección de los derechos individuales y colectivos, con la aspiración a transformar no solo el entorno académico universitario, sino también a que sirva como ejemplo para otras instituciones educativas en Colombia. El trabajo pretende usar para su desarrollo, las técnicas de procesamiento de lenguaje natural y las tecnologías de trata miento de datos teniendo en cuenta la normatividad de la privacidad de datos.</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>The project aims to develop a web-based software prototype for analyzing and evaluating the exposure of sensitive and non-sensitive data on Instagram, which is a web application. The novelty lies in the web product itself, not just the back-office functionality.</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Web Scraping, campus universitario, privacidad de datos, redes sociales</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:19+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2025S12</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>DISEÑO DE UN FORMULARIO WEB PARA LA MEJORA DEL PROCESO DE ONBOARDING Y VALIDACIÓN DE IDENTIDAD EN TRUORA MODALIDAD PASANTÍA</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Lenguaje Golang, MOAT, formulario web, constructor digital</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Este documento detalla el diseño e implementación de un constructor de formularios web en Truora, una empresa tecnológica dedicada a la validación de identidad digital y prevención de fraude. Se identificó la necesidad de esta herramienta debido a que los clientes debían recurrir a proveedores externos para la creación de formularios, lo que impedía a Truora centralizar la captura de información valiosa para el perfilamiento de usuarios. El proyecto se enmarca en la estrategia de Truora para 2024, buscando consolidar su posición como proveedor integral. El alcance incluyo todas las etapas de desarrollo del software, desde el levantamiento detallado de requisitos, el diseño de la arquitectura y la base de datos (utilizando AWS y DynamoDB), hasta el desarrollo del constructor de formularios web con tecnologías como Go (Golang) para el backend y Vue.js 3, TypeScript, Flowbite y Tailwind CSS para el frontend. Se siguió una metodología Scrumban, con colaboración cercana con el equipo de producto y UI/UX. Se desarrolló un Form Builder que permite la creación de secciones y preguntas con diversos tipos de input, reordenamiento de campos y validaciones configurables. Se estableció un flujo para el almacenamiento y consulta de respuestas, visibles en el dashboard de Truora. La validación del funcionamiento e integración se realizó a través de pruebas unitarias y funcionales, tanto en el frontend como en el backend, asegurando la compatibilidad con los sistemas existentes de Truora. Finalmente, se procedió al despliegue y monitoreo en el entorno de producción de AWS.</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>The project involves designing and implementing a web form builder for Truora, an enterprise that requires centralized data capture for user profiling. The system is developed using various technologies such as Go (Golang), Vue.js 3, TypeScript, Flowbite, and Tailwind CSS.</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>formulario web, constructor digital</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:23+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2025S13</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE APLICACIÓN WEB PARA LA GESTIÓN DE PROYECTOS ÁGILES EN DESARROLLO DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Aplicación web, gestión de proyectos, SCRUM, Kanban, código abierto.</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>En el entorno actual del desarrollo de software, la implementación efectiva de metodologías agiles resulta fundamental para el éxito de los proyectos. Sin embargo, muchas de las herramientas existentes presentan limitaciones en sus versiones gratuitas, lo que afecta especialmente a estudiantes y desarrolladores independientes con recursos limitados. En respuesta a esta problemática, se desarrolló una aplicación web de gestión de proyectos ágil, enfocada en ofrecer una solución gratuita, accesible y funcional. La plataforma permitió la creación y gestión de tableros Kanban, la generación de in formes del backlog, la integración de roles como Product Owner, Scrum Master y Team Member, y la creación de equipos. Además, incluyó funcionalidades como chat integrado, Planning Poker y una interfaz responsive adaptable a distintos dispositivos. El sistema fue diseñado bajo principios de usabilidad y escalabilidad, y se validó mediante pruebas funcionales. Esta herramienta demostró ser una alternativa eficaz frente a soluciones comerciales, permitiendo a equipos agiles mejorar su productividad y coordinación sin restricciones de acceso ni costo. Adicionalmente, la aplicación podría representar una herramienta valiosa en el entorno académico, especialmente en programas como Ingeniería de Sistemas, donde su uso puede ser integrado en cursos relacionados con el desarrollo de software, metodologías agiles o trabajo colaborativo.</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>The project developed a web application for agile project management in software development, with features such as Kanban boards, backlog reports, and integrated roles.</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Aplicación web, gestión de proyectos, SCRUM, Kanban</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:26+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2025S14</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SISTEMA DE RECONOCIMIENTO DE GESTOS DE MANO EN TIEMPO REAL PARA LA INTERACCIÓN HUMANO-COMPUTADORA</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Interación humano maquína, sistema en tiempo real, reconocimiento de gestos, visión por computador, seguimiento, accesibilidad, clasificación.</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>El presente trabajo se centró en el desarrollo de GestOS, un prototipo de reconocimiento de gestos de mano en tiempo real orientado a mejorar la interacción humano-computadora. Su propósito fue ofrecer una alternativa más accesible e inclusiva a los métodos tradicionales de entrada, como el teclado y el mouse, beneficiando tanto a personas con discapacidades como a quienes buscan nuevas formas de interacción. GestOS se construyó con una arquitectura modular compuesta por cuatro capas: presentación (React, TypeScript y Tailwind CSS), aplicación (Electron y Node.js), lógica de negocio (Python, MediaPipe y OpenCV) y acceso al sistema (PyAutoGUI, pynput y otras librerías). Este diseño permitió mantener una estructura escalable, estable y de fácil mantenimiento. El sistema emplea un enfoque híbrido que combina el análisis de puntos clave de la mano con modelos de aprendizaje automático, logrando reconocer siete gestos principales y algunos adicionales con una precisión cercana al 90%. Para evaluar su funcionamiento, se realizaron pruebas funcionales, de rendimiento y de accesibilidad con 43 usuarios, basadas en las normas WCAG 2.1 (nivel AA). Los resultados fueron positivos, aunque se identificaron áreas de mejora, como el rendimiento en condiciones de baja iluminación y la personalización de gestos. GestOS demuestra que la visión artificial puede contribuir significativamente a crear interfaces más naturales e inclusivas. A futuro, se plantea mejorar la precisión, la velocidad de respuesta y permitir el entrenamiento personalizado de gestos, fortaleciendo así la accesibilidad tecnológica.</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Computer vision</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>The project focuses on developing a real-time gesture recognition system using computer vision techniques, with the goal of improving human-computer interaction.</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>reconocimiento de gestos, visión por computador</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:29+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2025S15</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PLUGIN PARA LA GESTIÓN DE AMBIENTACIÓN EN ESCENARIOS DE VIDEOJUEGOS UTILIZANDO COMPUTACIÓN EMOCIONAL</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Interacción humano computadora, videojuegos, experiencia emocional, Prototipo integrado en Unity, computación emocional.</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Este trabajo de grado tuvo como objetivo desarrollar un plugin innovador para la gestión emocional de la ambientación en videojuegos, basado en los principios de la computación emocional. En los videojuegos actuales, la ambientación influye directamente en la experiencia emocional, la inmersión y la toma de decisiones del jugador. Por ello, se propuso una herramienta capaz de modificar dinámicamente elementos ambientales, especialmente la iluminación, según las emociones del usuario, generando experiencias más personalizadas e inmersivas. Se construyó un prototipo funcional integrado en Unity, diseñado con un enfoque modular y ligero para facilitar su integración en distintos proyectos sin afectar el rendimiento. La validación se realizó mediante una evaluación con usuarios, quienes visualizaron un video demostrativo y respondieron una encuesta sobre su percepción emocional. Los resultados mostraron que la mayoría identificó correctamente las atmósferas emocionales basadas en la iluminación y valoró positivamente su impacto en la narrativa y la experiencia de juego. El proyecto demostró que es posible modular la experiencia emocional del jugador mediante iluminación controlada, sin alterar la arquitectura ni la narrativa explícita. Además, evidenció que las emociones básicas como alegría y tristeza se interpretan con mayor consistencia, mientras que las más complejas requieren mayor contextualización. Finalmente, se concluyó que la iluminación puede actuar como un canal narrativo autónomo, capaz de evocar emociones y enriquecer la experiencia del jugador, aportando así al avance del campo de la computación emocional aplicada a los videojuegos.</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Serious games</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>The project involves developing a plugin for video game environments that uses emotional computing to modify ambient elements, such as lighting, based on the player's emotions, creating a more personalized and immersive experience.</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>videojuegos, computación emocional</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:33+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2025S16</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>APLICACIÓN WEB DE ATENCIÓN PARA CONSULTAS DE PROCEDIMIENTOS ADMINISTRATIVOS Y PREGUNTAS FRECUENTES CON INTEGRACIÓN DE UN CHATBOT</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Procesamiento Lenguaje Natural, chatbot, inteligencia artificial, procedimientos administrativos.</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>En este proyecto de trabajo de grado, se desarrolló una aplicación web con información para atender preguntas frecuentes y consultas acerca de algunos procesos administrativos que puedan tener los estudiantes de ingeniería de sistemas de la sede Tuluá, con el apoyo de un asistente virtual (chatbot) para la resolución de dudas acerca de la información requerida, con el fin de reducir el tiempo que usa el personal administrativo en la atención de estos asuntos, incrementando la productividad de los mismos y a su vez dar una respuesta oportuna a dudas o preguntas frecuentes de los alumnos evitando que se desplacen a la oficina o en contra parte, que envíen correos que debido al gran volumen de estos, la respuesta tardará algo de tiempo en llegar. En el desarrollo del proyecto se utilizó inteligencia artificial (IA) para la creación del chatbot incorporando técnicas de procesamiento de lenguaje natural (PLN) para que los estudiantes tengan una interacción fluida y facilidad para dar respuesta a sus cuestionamientos. Además, se adoptó un enfoque web, considerando que actualmente las personas utilizan cada vez más dispositivos inteligentes. Desarrollar una aplicación nativa para cada plataforma puede ser una tarea ardua. Este problema puede ser mitigado significativamente mediante el uso de tecnologías web, ya que permiten que la aplicación sea accesible desde una amplia gama de dispositivos con el único requisito de contar con un navegador web compatible.</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>The project developed a web application with a chatbot to answer frequent questions and administrative procedures, using natural language processing techniques and artificial intelligence.</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Procesamiento Lenguaje Natural, chatbot, inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:36+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2025S17</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>DISEÑO E IMPLEMENTACIÓN DE UN LAUNCHER ANDROID ENFOCADO A COMBATIR LA PROCRASTINACIÓN POR EL USO EXCESIVO DEL SMARTPHONE EN ESTUDIANTES DE PREGRADO DE LA UNIVERSIDAD DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Mitigar distracciones, procrastinación, smartphone, telefonos android, launcher.</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Los estudiantes universitarios que hacen un uso excesivo y/o inadecuado del smartphone tienen un menor rendimiento académico e insatisfacción al no gestionar adecuadamente su tiempo e incumplir los plazos de sus actividades pendientes. Dado que el ecosistema de los teléfonos móviles y sus aplicaciones incentiva a pasar el mayor tiempo posible usándolos, se propone desarrollar una pantalla de inicio (launcher) para teléfonos Android que apunte a reducir la procrastinación mediante una interfaz mínimamente llamativa, a mitigar las distracciones y a gestionar mejor el tiempo invertido dentro de las aplicaciones, principalmente en horarios donde se requiera total disposición a una actividad concreta.</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Mobile applications</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>The project focuses on designing and implementing an Android launcher to combat procrastination among university students, which is a mobile application.</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>procrastinación, smartphone, launcher</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:39+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2025S18</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>SISTEMA DE OPTIMIZACIÓN DE LA PROGRAMACIÓN ACADÉMICA PARA LA SECCIONAL BUGA</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Sistema de Optimización, programación academica, gestión horaria.</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>El problema estudiado es la gestión ineficiente de horarios y recursos en instituciones educativas, lo que puede provocar conflictos de horarios y una utilización subóptima de los recursos disponibles. Se estudia con el fin de mejorar la eficiencia y la organización en la programación académica. El sistema utiliza algoritmos avanzados para optimizar la distribución de clases, estos algoritmos tienen en cuenta múltiples factores, como la disponibilidad de docentes, requerimientos de asignaturas y características de los salones. Proporcionan una programación académica óptima, minimizando conflictos de horarios y maximizando la utilización de recursos disponibles, a través de una interfaz que permita a los administradores ingresar información relevante. Los resultados obtenidos demuestran que el Sistema de Optimización de Programación Académica es eficaz para mejorar la gestión de horarios y recursos en instituciones educativas. Esto significa que se puede lograr una distribución equitativa de las clases y una utilización más eficiente de los recursos disponibles, lo que contribuye a un funcionamiento más fluido y productivo.</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Enterprise information systems</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>The project is focused on developing an optimization system for academic programming in the Buga section, which involves managing schedules and resources efficiently. The system uses advanced algorithms to optimize class distribution, taking into account multiple factors such as teacher availability, subject requirements, and classroom characteristics.</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>Sistema de Optimización, programación academica, gestión horaria</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2025S19</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PROTOTIPO DE SOFTWARE USANDO LA GAMIFICACIÓN PARA El APOYO DEL APRENDIZAJE EN LA ASIGNATURA DE CIENCIAS SOCIALES Y EN LA CULTURA GENERAL COLOMBIANA EN NIÑOS DE 5TO GRADO DE PRIMARIA</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Videojuegos, gamificación, ciencias sociales, aprendizaje.</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Este trabajo de grado presenta el desarrollo de un prototipo de videojuego junto a elementos de gamificación, aplicado en el área de Ciencias Sociales y en las competencias de cultura general colombiana, diseñado específicamente para estudiantes de quinto grado de primaria. La propuesta surge como respuesta a la necesidad de generar herramientas innovadoras que despierten el interés de los niños y apoyen su aprendizaje. Durante la etapa de investigación, se realizó un proceso de recopilación y análisis de contenidos educativos a partir de fuentes confiables, planes de estudio oficiales y materiales de libre acceso en línea, ante la dificultad de obtener insumos directamente de las instituciones educativas. Esto permitió construir diálogos, escenarios y dinámicas representativas de cuatro regiones del país: Caribe, Pacífica, Orinoquía y Amazonía. La implementación técnica se llevó a cabo utilizando un motor gráfico apoyado en herramientas para el modelado 3D, las animaciones de personajes, la generación de texturas y bibliotecas de sonido de libre uso. El videojuego fue diseñado con una estructura modular de misiones, cada una con objetivos específicos y personajes interactivos que fomentan la exploración. La fase de pruebas incluyó la aplicación del prototipo en un grupo real de estudiantes, mediante observación directa y entrevistas estructuradas tanto a los niños como a su docente. Los resultados muestran un alto nivel de motivación, participación activa y comprensión temática por parte de los estudiantes, validando la efectividad del enfoque lúdico para el aprendizaje de las Ciencias Sociales y la cultura general. Este proyecto demostró la viabilidad técnica y pedagógica de integrar el desarrollo de software con la educación primaria, proponiendo un modelo replicable que puede ser ampliado y mejorado en futuras investigaciones. Así, se reafirma el potencial de los videojuegos como herramientas educativas valiosas en contextos escolares</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Gamification</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>The project aims to develop a software prototype using gamification to support learning in social sciences and Colombian culture for primary school students, indicating that gamification is the central contribution.</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>gamificación, aprendizaje</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:46+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2025S20</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PROTOTIPO DE APLICACIÓN WEB PARA LA IMPLEMENTACIÓN DE UN SISTEMA DE RECOMENDACIÓN DE ROPA BASADO EN EL BIENESTAR EMOCIONAL DEL USUARIO MEDIANTE LA INTEGRACIÓN DE LA ECONOMÍA CONDUCTUAL</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Clothing recommendation system, Prototype web application, Human computer interaction, user interfaces, Sentiment analysis.</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>En la ingeniería de sistemas, el diseño de aplicaciones web suele centrarse en aspectos técnicos, dejando de lado las emociones del usuario. Esta limitación es particularmente evidente en las plataformas de recomendación de ropa, donde la falta de empatía genera experiencias impersonales y desconectadas emocionalmente. Como resultado, se afecta la toma de decisiones, la fidelización y la satisfacción de los usuarios. Este trabajo de grado propuso el desarrollo de un prototipo de aplicación web que incorpora el análisis emocional del usuario y principios de la Economía Conductual para ofrecer recomendaciones de ropa más humanas, personalizadas y emocionalmente relevantes. El objetivo no fue solo facilitar la elección de una prenda, sino también atender el estado emocional de cada individuo y reconocer su influencia en la interacción con la tecnología. La propuesta se construyó desde un enfoque interdisciplinario, integrando psicología del usuario, interacción humano-computadora y bienestar digital. Se trabajó con conceptos como inteligencia emocional, modelado de estados afectivos y toma de decisiones influenciada por emociones. Los resultados del prototipo demostraron que incluir elementos emocionales mejora la experiencia digital, fomenta la personalización y permite construir plataformas más sensibles y alineadas con las necesidades reales del usuario. Este enfoque contribuye a una visión más humana de la tecnología y plantea nuevas posibilidades para el diseño digital en la moda y otros sectores.</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Web applications</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Recommender systems</t>
+        </is>
+      </c>
+      <c r="H248" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>The project proposes the development of a web application that incorporates emotional analysis and principles of Behavioral Economics to offer personalized and emotionally relevant clothing recommendations.</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>Clothing recommendation system, Prototype web application</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2025S21</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SISTEMA DE DETECCION TEMPRANA DE SOFTWARE MALINTENCIONADO POR MEDIO DE COMPORTAMIENTOS ANÓMALOS EN WINDOWS 10</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Ransomware de cifrado, ciberseguridad, ciberataque, integridad de datos.</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Este proyecto se realizó con el objetivo de desarrollar un prototipo de sistema para la detección temprana de comportamientos anómalos en el sistema operativo Windows 10, con el fin de prevenir posibles ataques de ransomware de cifrado y la pérdida de datos que estos conllevan. La justificación de este trabajo radica en la necesidad de herramientas que permitan identificar patrones de comportamiento sospechosos en sistemas informáticos, específicamente en Windows 10, lo que posibilitará recolectar la información necesaria para detectar cuándo se está ejecutando un ataque de ransomware y desplegar una respuesta efectiva en el sistema operativo, reduciendo significativamente el riesgo de pérdida de información. Finalmente, se consiguió desarrollar un prototipo de detección funcional con un alto nivel de asertividad en la detección de comportamientos anómalos por medio de la aplicación de puntaje por entropía, lo cuál cumple con los objetivos planteados.</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>metadata_only</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>The project aims to develop a system for early detection of ransomware attacks by identifying suspicious behavior in Windows 10, which aligns with the broader goal of cybersecurity.</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>ciberseguridad, ransomware de cifrado</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:34:52+00:00</t>
         </is>
       </c>
     </row>
